--- a/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF25CE44-A0D1-4F13-AC92-8FBD329C08D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D0F040-DDB6-4AD9-8786-156072A174EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards " sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="281">
   <si>
     <t>Component list</t>
   </si>
@@ -851,6 +851,21 @@
   </si>
   <si>
     <t>Karen Quote</t>
+  </si>
+  <si>
+    <t>Available stock in Karen House 1500 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LULU Quote </t>
+  </si>
+  <si>
+    <t>Karan Quote</t>
+  </si>
+  <si>
+    <t>LULU Quote</t>
+  </si>
+  <si>
+    <t>Available stock in LULU House 1661 pcs</t>
   </si>
 </sst>
 </file>
@@ -862,7 +877,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,6 +1058,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1358,7 +1381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1656,6 +1679,12 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3485,10 +3514,12 @@
         <f t="shared" si="2"/>
         <v>360</v>
       </c>
-      <c r="R29" s="46"/>
+      <c r="R29" s="89" t="s">
+        <v>275</v>
+      </c>
       <c r="S29" s="47"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="37">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -3528,14 +3559,22 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N30" s="61"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="70"/>
+      <c r="N30" s="61">
+        <v>90</v>
+      </c>
+      <c r="O30" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="P30" s="70">
+        <v>2</v>
+      </c>
       <c r="Q30" s="70">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R30" s="67"/>
+        <v>180</v>
+      </c>
+      <c r="R30" s="95" t="s">
+        <v>275</v>
+      </c>
       <c r="S30" s="70"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4484,7 +4523,7 @@
       <c r="R47" s="46"/>
       <c r="S47" s="47"/>
     </row>
-    <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="37">
         <f t="shared" si="0"/>
@@ -4511,7 +4550,9 @@
       <c r="I48" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="J48" s="61"/>
+      <c r="J48" s="61" t="s">
+        <v>229</v>
+      </c>
       <c r="K48" s="68" t="s">
         <v>229</v>
       </c>
@@ -4525,16 +4566,22 @@
       <c r="N48" s="61">
         <v>22</v>
       </c>
-      <c r="O48" s="69"/>
-      <c r="P48" s="70"/>
+      <c r="O48" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" s="70">
+        <v>7.3</v>
+      </c>
       <c r="Q48" s="70">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="67"/>
+        <v>160.6</v>
+      </c>
+      <c r="R48" s="95" t="s">
+        <v>275</v>
+      </c>
       <c r="S48" s="70"/>
     </row>
-    <row r="49" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="37">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -4561,7 +4608,9 @@
       <c r="I49" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="J49" s="45"/>
+      <c r="J49" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="K49" s="58" t="s">
         <v>229</v>
       </c>
@@ -4575,13 +4624,19 @@
       <c r="N49" s="45">
         <v>82</v>
       </c>
-      <c r="O49" s="62"/>
-      <c r="P49" s="47"/>
+      <c r="O49" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="P49" s="47">
+        <v>4.2</v>
+      </c>
       <c r="Q49" s="47">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="46"/>
+        <v>344.40000000000003</v>
+      </c>
+      <c r="R49" s="89" t="s">
+        <v>275</v>
+      </c>
       <c r="S49" s="47"/>
     </row>
     <row r="50" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4717,7 +4772,7 @@
       <c r="P52" s="105"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
-        <v>1591.529</v>
+        <v>2276.5289999999995</v>
       </c>
       <c r="R52" s="100"/>
       <c r="S52" s="101"/>
@@ -4743,7 +4798,7 @@
       <c r="P53" s="105"/>
       <c r="Q53" s="57">
         <f>Q52/20</f>
-        <v>79.576449999999994</v>
+        <v>113.82644999999998</v>
       </c>
       <c r="R53" s="102"/>
       <c r="S53" s="103"/>
@@ -6184,7 +6239,7 @@
       <c r="R29" s="46"/>
       <c r="S29" s="47"/>
     </row>
-    <row r="30" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" s="64" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="63"/>
       <c r="B30" s="37">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -6208,8 +6263,12 @@
       <c r="H30" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
+      <c r="I30" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>229</v>
+      </c>
       <c r="K30" s="68" t="s">
         <v>229</v>
       </c>
@@ -6220,14 +6279,22 @@
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-      <c r="N30" s="61"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="70"/>
+      <c r="N30" s="61">
+        <v>4050</v>
+      </c>
+      <c r="O30" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="P30" s="70">
+        <v>1.01</v>
+      </c>
       <c r="Q30" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R30" s="67"/>
+        <v>4090.5</v>
+      </c>
+      <c r="R30" s="95" t="s">
+        <v>276</v>
+      </c>
       <c r="S30" s="70"/>
     </row>
     <row r="31" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6930,9 +6997,11 @@
       <c r="H43" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="I43" s="45"/>
+      <c r="I43" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="J43" s="45" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="K43" s="58" t="s">
         <v>229</v>
@@ -6944,14 +7013,22 @@
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
-      <c r="N43" s="45"/>
-      <c r="O43" s="62"/>
-      <c r="P43" s="47"/>
+      <c r="N43" s="45">
+        <v>8020</v>
+      </c>
+      <c r="O43" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="P43" s="47">
+        <v>2.206</v>
+      </c>
       <c r="Q43" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R43" s="46"/>
+        <v>17692.12</v>
+      </c>
+      <c r="R43" s="106" t="s">
+        <v>277</v>
+      </c>
       <c r="S43" s="47"/>
     </row>
     <row r="44" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7209,7 +7286,9 @@
       <c r="I48" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="J48" s="61"/>
+      <c r="J48" s="61" t="s">
+        <v>229</v>
+      </c>
       <c r="K48" s="68" t="s">
         <v>229</v>
       </c>
@@ -7220,14 +7299,22 @@
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N48" s="61"/>
-      <c r="O48" s="69"/>
-      <c r="P48" s="70"/>
+      <c r="N48" s="61">
+        <v>1020</v>
+      </c>
+      <c r="O48" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" s="70">
+        <v>4.8</v>
+      </c>
       <c r="Q48" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="67"/>
+        <v>4896</v>
+      </c>
+      <c r="R48" s="95" t="s">
+        <v>273</v>
+      </c>
       <c r="S48" s="70"/>
     </row>
     <row r="49" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7257,7 +7344,9 @@
       <c r="I49" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="J49" s="45"/>
+      <c r="J49" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="K49" s="58" t="s">
         <v>229</v>
       </c>
@@ -7268,14 +7357,22 @@
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-      <c r="N49" s="45"/>
-      <c r="O49" s="62"/>
-      <c r="P49" s="47"/>
+      <c r="N49" s="45">
+        <v>4020</v>
+      </c>
+      <c r="O49" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="P49" s="47">
+        <v>1.9</v>
+      </c>
       <c r="Q49" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="46"/>
+        <v>7638</v>
+      </c>
+      <c r="R49" s="106" t="s">
+        <v>277</v>
+      </c>
       <c r="S49" s="47"/>
     </row>
     <row r="50" spans="1:19" s="64" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7411,7 +7508,7 @@
       <c r="P52" s="105"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
-        <v>36042.976999999992</v>
+        <v>70359.596999999994</v>
       </c>
       <c r="R52" s="100"/>
       <c r="S52" s="101"/>
@@ -7437,7 +7534,7 @@
       <c r="P53" s="105"/>
       <c r="Q53" s="57">
         <f>Q52/1000</f>
-        <v>36.042976999999993</v>
+        <v>70.359596999999994</v>
       </c>
       <c r="R53" s="102"/>
       <c r="S53" s="103"/>
@@ -9025,19 +9122,25 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="N29" s="45"/>
+      <c r="N29" s="45">
+        <v>40100</v>
+      </c>
       <c r="O29" s="62" t="s">
         <v>235</v>
       </c>
-      <c r="P29" s="47"/>
+      <c r="P29" s="47">
+        <v>0.72</v>
+      </c>
       <c r="Q29" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R29" s="46"/>
+        <v>28872</v>
+      </c>
+      <c r="R29" s="89" t="s">
+        <v>278</v>
+      </c>
       <c r="S29" s="47"/>
     </row>
-    <row r="30" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" s="64" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="63"/>
       <c r="B30" s="37">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -9061,8 +9164,12 @@
       <c r="H30" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
+      <c r="I30" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>229</v>
+      </c>
       <c r="K30" s="68" t="s">
         <v>229</v>
       </c>
@@ -9073,14 +9180,22 @@
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="N30" s="61"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="70"/>
+      <c r="N30" s="61">
+        <v>20100</v>
+      </c>
+      <c r="O30" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="P30" s="70">
+        <v>1</v>
+      </c>
       <c r="Q30" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R30" s="67"/>
+        <v>20100</v>
+      </c>
+      <c r="R30" s="107" t="s">
+        <v>280</v>
+      </c>
       <c r="S30" s="70"/>
     </row>
     <row r="31" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9684,7 +9799,9 @@
         <f t="shared" si="3"/>
         <v>111.1</v>
       </c>
-      <c r="R41" s="89"/>
+      <c r="R41" s="89" t="s">
+        <v>278</v>
+      </c>
       <c r="S41" s="47"/>
     </row>
     <row r="42" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9740,10 +9857,12 @@
         <f t="shared" si="3"/>
         <v>15662.4</v>
       </c>
-      <c r="R42" s="67"/>
+      <c r="R42" s="95" t="s">
+        <v>278</v>
+      </c>
       <c r="S42" s="70"/>
     </row>
-    <row r="43" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="63"/>
       <c r="B43" s="37">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -9767,9 +9886,11 @@
       <c r="H43" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="I43" s="45"/>
+      <c r="I43" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="J43" s="45" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="K43" s="58" t="s">
         <v>229</v>
@@ -9781,14 +9902,22 @@
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="N43" s="45"/>
-      <c r="O43" s="62"/>
-      <c r="P43" s="47"/>
+      <c r="N43" s="45">
+        <v>40100</v>
+      </c>
+      <c r="O43" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="P43" s="47">
+        <v>2.206</v>
+      </c>
       <c r="Q43" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R43" s="46"/>
+        <v>88460.599999999991</v>
+      </c>
+      <c r="R43" s="106" t="s">
+        <v>279</v>
+      </c>
       <c r="S43" s="47"/>
     </row>
     <row r="44" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10015,7 +10144,7 @@
       <c r="R47" s="89"/>
       <c r="S47" s="47"/>
     </row>
-    <row r="48" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="63"/>
       <c r="B48" s="37">
         <f t="shared" si="0"/>
@@ -10042,7 +10171,9 @@
       <c r="I48" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="J48" s="61"/>
+      <c r="J48" s="61" t="s">
+        <v>229</v>
+      </c>
       <c r="K48" s="68" t="s">
         <v>229</v>
       </c>
@@ -10053,17 +10184,25 @@
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="N48" s="61"/>
-      <c r="O48" s="69"/>
-      <c r="P48" s="70"/>
+      <c r="N48" s="61">
+        <v>5020</v>
+      </c>
+      <c r="O48" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" s="70">
+        <v>3.383</v>
+      </c>
       <c r="Q48" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="67"/>
+        <v>16982.66</v>
+      </c>
+      <c r="R48" s="107" t="s">
+        <v>279</v>
+      </c>
       <c r="S48" s="70"/>
     </row>
-    <row r="49" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="63"/>
       <c r="B49" s="37">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -10090,7 +10229,9 @@
       <c r="I49" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="J49" s="45"/>
+      <c r="J49" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="K49" s="58" t="s">
         <v>229</v>
       </c>
@@ -10101,14 +10242,22 @@
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="N49" s="45"/>
-      <c r="O49" s="62"/>
-      <c r="P49" s="47"/>
+      <c r="N49" s="45">
+        <v>20050</v>
+      </c>
+      <c r="O49" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="P49" s="47">
+        <v>1.2649999999999999</v>
+      </c>
       <c r="Q49" s="47">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="46"/>
+        <v>25363.249999999996</v>
+      </c>
+      <c r="R49" s="106" t="s">
+        <v>279</v>
+      </c>
       <c r="S49" s="47"/>
     </row>
     <row r="50" spans="1:19" s="64" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10244,7 +10393,7 @@
       <c r="P52" s="105"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
-        <v>125338.65299999999</v>
+        <v>305117.163</v>
       </c>
       <c r="R52" s="100"/>
       <c r="S52" s="101"/>
@@ -10270,7 +10419,7 @@
       <c r="P53" s="105"/>
       <c r="Q53" s="57">
         <f>Q52/5000</f>
-        <v>25.067730599999997</v>
+        <v>61.0234326</v>
       </c>
       <c r="R53" s="102"/>
       <c r="S53" s="103"/>

--- a/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D0F040-DDB6-4AD9-8786-156072A174EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999F553D-8BEC-4F43-9A85-8EC6EA44CE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards " sheetId="1" r:id="rId1"/>
@@ -18,11 +18,24 @@
     <sheet name="5K Boards" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="281">
   <si>
     <t>Component list</t>
   </si>
@@ -1648,6 +1661,12 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1679,12 +1698,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2169,15 +2182,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="97"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2227,7 +2240,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="98"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2252,7 +2265,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="99"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2277,7 +2290,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="99"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2298,7 +2311,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="99"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2319,7 +2332,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="99"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2340,7 +2353,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="99"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4174,21 +4187,19 @@
         <v>20</v>
       </c>
       <c r="N41" s="45">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="O41" s="62" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P41" s="47">
-        <v>5.8200000000000002E-2</v>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="Q41" s="47">
         <f t="shared" si="2"/>
-        <v>1.2804</v>
-      </c>
-      <c r="R41" s="89" t="s">
-        <v>275</v>
-      </c>
+        <v>1.728</v>
+      </c>
+      <c r="R41" s="89"/>
       <c r="S41" s="47"/>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4765,17 +4776,17 @@
       <c r="K52" s="36"/>
       <c r="L52" s="60"/>
       <c r="M52" s="36"/>
-      <c r="N52" s="104" t="s">
+      <c r="N52" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="O52" s="105"/>
-      <c r="P52" s="105"/>
+      <c r="O52" s="107"/>
+      <c r="P52" s="107"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
-        <v>2276.5289999999995</v>
-      </c>
-      <c r="R52" s="100"/>
-      <c r="S52" s="101"/>
+        <v>2276.9765999999995</v>
+      </c>
+      <c r="R52" s="102"/>
+      <c r="S52" s="103"/>
     </row>
     <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -4791,17 +4802,17 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
-      <c r="N53" s="104" t="s">
+      <c r="N53" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="O53" s="105"/>
-      <c r="P53" s="105"/>
+      <c r="O53" s="107"/>
+      <c r="P53" s="107"/>
       <c r="Q53" s="57">
         <f>Q52/20</f>
-        <v>113.82644999999998</v>
-      </c>
-      <c r="R53" s="102"/>
-      <c r="S53" s="103"/>
+        <v>113.84882999999998</v>
+      </c>
+      <c r="R53" s="104"/>
+      <c r="S53" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4846,10 +4857,11 @@
     <hyperlink ref="O51" r:id="rId32" xr:uid="{71472283-ADCE-419D-B345-3F78D4C9B4A1}"/>
     <hyperlink ref="O15" r:id="rId33" xr:uid="{386A98B2-E463-46C3-98CA-031EE3ACAF7E}"/>
     <hyperlink ref="O18" r:id="rId34" xr:uid="{3F640406-EF82-415C-B941-ACDE17CD6FD1}"/>
+    <hyperlink ref="O41" r:id="rId35" xr:uid="{43DD3F14-DD7D-4C17-951A-197F63191CA8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
-  <drawing r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
+  <drawing r:id="rId37"/>
 </worksheet>
 </file>
 
@@ -4889,15 +4901,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="97"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4947,7 +4959,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="98"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4972,7 +4984,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="99"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4997,7 +5009,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="99"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5018,7 +5030,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="99"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5039,7 +5051,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="99"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5060,7 +5072,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="99"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -7026,7 +7038,7 @@
         <f t="shared" si="3"/>
         <v>17692.12</v>
       </c>
-      <c r="R43" s="106" t="s">
+      <c r="R43" s="96" t="s">
         <v>277</v>
       </c>
       <c r="S43" s="47"/>
@@ -7370,7 +7382,7 @@
         <f t="shared" si="3"/>
         <v>7638</v>
       </c>
-      <c r="R49" s="106" t="s">
+      <c r="R49" s="96" t="s">
         <v>277</v>
       </c>
       <c r="S49" s="47"/>
@@ -7501,17 +7513,17 @@
       <c r="K52" s="36"/>
       <c r="L52" s="60"/>
       <c r="M52" s="36"/>
-      <c r="N52" s="104" t="s">
+      <c r="N52" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="O52" s="105"/>
-      <c r="P52" s="105"/>
+      <c r="O52" s="107"/>
+      <c r="P52" s="107"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
         <v>70359.596999999994</v>
       </c>
-      <c r="R52" s="100"/>
-      <c r="S52" s="101"/>
+      <c r="R52" s="102"/>
+      <c r="S52" s="103"/>
     </row>
     <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -7527,17 +7539,17 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
-      <c r="N53" s="104" t="s">
+      <c r="N53" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="O53" s="105"/>
-      <c r="P53" s="105"/>
+      <c r="O53" s="107"/>
+      <c r="P53" s="107"/>
       <c r="Q53" s="57">
         <f>Q52/1000</f>
         <v>70.359596999999994</v>
       </c>
-      <c r="R53" s="102"/>
-      <c r="S53" s="103"/>
+      <c r="R53" s="104"/>
+      <c r="S53" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7788,15 +7800,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="97"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -7846,7 +7858,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="98"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -7871,7 +7883,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="99"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -7896,7 +7908,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="99"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -7917,7 +7929,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="99"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -7938,7 +7950,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="99"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -7959,7 +7971,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="99"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -9193,7 +9205,7 @@
         <f t="shared" si="3"/>
         <v>20100</v>
       </c>
-      <c r="R30" s="107" t="s">
+      <c r="R30" s="97" t="s">
         <v>280</v>
       </c>
       <c r="S30" s="70"/>
@@ -9915,7 +9927,7 @@
         <f t="shared" si="3"/>
         <v>88460.599999999991</v>
       </c>
-      <c r="R43" s="106" t="s">
+      <c r="R43" s="96" t="s">
         <v>279</v>
       </c>
       <c r="S43" s="47"/>
@@ -10197,7 +10209,7 @@
         <f t="shared" si="3"/>
         <v>16982.66</v>
       </c>
-      <c r="R48" s="107" t="s">
+      <c r="R48" s="97" t="s">
         <v>279</v>
       </c>
       <c r="S48" s="70"/>
@@ -10255,7 +10267,7 @@
         <f t="shared" si="3"/>
         <v>25363.249999999996</v>
       </c>
-      <c r="R49" s="106" t="s">
+      <c r="R49" s="96" t="s">
         <v>279</v>
       </c>
       <c r="S49" s="47"/>
@@ -10386,17 +10398,17 @@
       <c r="K52" s="36"/>
       <c r="L52" s="60"/>
       <c r="M52" s="36"/>
-      <c r="N52" s="104" t="s">
+      <c r="N52" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="O52" s="105"/>
-      <c r="P52" s="105"/>
+      <c r="O52" s="107"/>
+      <c r="P52" s="107"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
         <v>305117.163</v>
       </c>
-      <c r="R52" s="100"/>
-      <c r="S52" s="101"/>
+      <c r="R52" s="102"/>
+      <c r="S52" s="103"/>
     </row>
     <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -10412,17 +10424,17 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
-      <c r="N53" s="104" t="s">
+      <c r="N53" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="O53" s="105"/>
-      <c r="P53" s="105"/>
+      <c r="O53" s="107"/>
+      <c r="P53" s="107"/>
       <c r="Q53" s="57">
         <f>Q52/5000</f>
         <v>61.0234326</v>
       </c>
-      <c r="R53" s="102"/>
-      <c r="S53" s="103"/>
+      <c r="R53" s="104"/>
+      <c r="S53" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999F553D-8BEC-4F43-9A85-8EC6EA44CE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCFF809-C5EF-4C85-917C-72CF641BD41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards " sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="283">
   <si>
     <t>Component list</t>
   </si>
@@ -749,9 +749,6 @@
   </si>
   <si>
     <t>C181312</t>
-  </si>
-  <si>
-    <t>C62892</t>
   </si>
   <si>
     <t>C2898996</t>
@@ -879,6 +876,15 @@
   </si>
   <si>
     <t>Available stock in LULU House 1661 pcs</t>
+  </si>
+  <si>
+    <t>C123008</t>
+  </si>
+  <si>
+    <t>UMH3NTN</t>
+  </si>
+  <si>
+    <t>C318893</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2207,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2226,7 +2232,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2251,7 +2257,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2496,7 +2502,7 @@
         <v>229</v>
       </c>
       <c r="J11" s="45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K11" s="58" t="s">
         <v>186</v>
@@ -2534,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" s="67" t="s">
         <v>61</v>
@@ -2548,7 +2554,9 @@
       <c r="H12" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="I12" s="61"/>
+      <c r="I12" s="61" t="s">
+        <v>229</v>
+      </c>
       <c r="J12" s="61" t="s">
         <v>176</v>
       </c>
@@ -2606,7 +2614,7 @@
         <v>229</v>
       </c>
       <c r="J13" s="45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K13" s="58" t="s">
         <v>188</v>
@@ -2700,7 +2708,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E15" s="45" t="s">
         <v>56</v>
@@ -2715,10 +2723,10 @@
         <v>155</v>
       </c>
       <c r="I15" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="J15" s="45" t="s">
         <v>268</v>
-      </c>
-      <c r="J15" s="45" t="s">
-        <v>269</v>
       </c>
       <c r="K15" s="58" t="s">
         <v>190</v>
@@ -2774,7 +2782,7 @@
         <v>229</v>
       </c>
       <c r="J16" s="61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K16" s="68" t="s">
         <v>191</v>
@@ -2830,7 +2838,7 @@
         <v>229</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K17" s="58" t="s">
         <v>192</v>
@@ -2868,7 +2876,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E18" s="67" t="s">
         <v>59</v>
@@ -2883,10 +2891,10 @@
         <v>159</v>
       </c>
       <c r="I18" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="J18" s="61" t="s">
         <v>270</v>
-      </c>
-      <c r="J18" s="61" t="s">
-        <v>271</v>
       </c>
       <c r="K18" s="68" t="s">
         <v>193</v>
@@ -2998,7 +3006,7 @@
         <v>229</v>
       </c>
       <c r="J20" s="61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K20" s="68" t="s">
         <v>195</v>
@@ -3166,7 +3174,7 @@
         <v>229</v>
       </c>
       <c r="J23" s="45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K23" s="58" t="s">
         <v>193</v>
@@ -3528,7 +3536,7 @@
         <v>360</v>
       </c>
       <c r="R29" s="89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S29" s="47"/>
     </row>
@@ -3586,7 +3594,7 @@
         <v>180</v>
       </c>
       <c r="R30" s="95" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S30" s="70"/>
     </row>
@@ -3726,10 +3734,10 @@
         <v>162</v>
       </c>
       <c r="I33" s="78" t="s">
+        <v>242</v>
+      </c>
+      <c r="J33" s="78" t="s">
         <v>243</v>
-      </c>
-      <c r="J33" s="78" t="s">
-        <v>244</v>
       </c>
       <c r="K33" s="80" t="s">
         <v>197</v>
@@ -3785,7 +3793,7 @@
         <v>229</v>
       </c>
       <c r="J34" s="61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K34" s="68" t="s">
         <v>198</v>
@@ -3841,7 +3849,7 @@
         <v>229</v>
       </c>
       <c r="J35" s="45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K35" s="58" t="s">
         <v>199</v>
@@ -3951,7 +3959,7 @@
       </c>
       <c r="I37" s="45"/>
       <c r="J37" s="45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K37" s="58" t="s">
         <v>201</v>
@@ -3989,7 +3997,7 @@
         <v>208</v>
       </c>
       <c r="D38" s="71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E38" s="67" t="s">
         <v>80</v>
@@ -4063,7 +4071,7 @@
         <v>229</v>
       </c>
       <c r="J39" s="45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K39" s="58" t="s">
         <v>203</v>
@@ -4174,7 +4182,7 @@
         <v>229</v>
       </c>
       <c r="J41" s="45" t="s">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="K41" s="58" t="s">
         <v>229</v>
@@ -4340,7 +4348,7 @@
         <v>229</v>
       </c>
       <c r="J44" s="61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>229</v>
@@ -4392,8 +4400,12 @@
       <c r="H45" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
+      <c r="I45" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="J45" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="K45" s="58" t="s">
         <v>229</v>
       </c>
@@ -4418,7 +4430,7 @@
         <v>277.2</v>
       </c>
       <c r="R45" s="89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S45" s="47"/>
     </row>
@@ -4438,7 +4450,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="61" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G46" s="67" t="s">
         <v>118</v>
@@ -4494,19 +4506,19 @@
         <v>89</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="G47" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="G47" s="73" t="s">
         <v>119</v>
       </c>
       <c r="H47" s="45" t="s">
         <v>168</v>
       </c>
       <c r="I47" s="45" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="J47" s="45" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K47" s="58" t="s">
         <v>229</v>
@@ -4519,17 +4531,17 @@
         <v>20</v>
       </c>
       <c r="N47" s="45">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O47" s="62" t="s">
         <v>227</v>
       </c>
       <c r="P47" s="47">
-        <v>5.5800000000000002E-2</v>
+        <v>0.10639999999999999</v>
       </c>
       <c r="Q47" s="47">
         <f t="shared" si="2"/>
-        <v>1.6740000000000002</v>
+        <v>2.6599999999999997</v>
       </c>
       <c r="R47" s="46"/>
       <c r="S47" s="47"/>
@@ -4588,7 +4600,7 @@
         <v>160.6</v>
       </c>
       <c r="R48" s="95" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S48" s="70"/>
     </row>
@@ -4646,7 +4658,7 @@
         <v>344.40000000000003</v>
       </c>
       <c r="R49" s="89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S49" s="47"/>
     </row>
@@ -4678,10 +4690,10 @@
         <v>229</v>
       </c>
       <c r="J50" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="K50" s="68" t="s">
         <v>239</v>
-      </c>
-      <c r="K50" s="68" t="s">
-        <v>240</v>
       </c>
       <c r="L50" s="61">
         <v>1</v>
@@ -4734,10 +4746,10 @@
         <v>229</v>
       </c>
       <c r="J51" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="K51" s="58" t="s">
         <v>241</v>
-      </c>
-      <c r="K51" s="58" t="s">
-        <v>242</v>
       </c>
       <c r="L51" s="75">
         <v>2</v>
@@ -4783,7 +4795,7 @@
       <c r="P52" s="107"/>
       <c r="Q52" s="56">
         <f>SUM(Q10:Q51)</f>
-        <v>2276.9765999999995</v>
+        <v>2277.9625999999998</v>
       </c>
       <c r="R52" s="102"/>
       <c r="S52" s="103"/>
@@ -4809,7 +4821,7 @@
       <c r="P53" s="107"/>
       <c r="Q53" s="57">
         <f>Q52/20</f>
-        <v>113.84882999999998</v>
+        <v>113.89812999999999</v>
       </c>
       <c r="R53" s="104"/>
       <c r="S53" s="105"/>
@@ -4828,36 +4840,36 @@
     <hyperlink ref="O26" r:id="rId3" xr:uid="{1FFF2F14-D016-403D-B7DE-3461C5CEE3CC}"/>
     <hyperlink ref="O28" r:id="rId4" xr:uid="{A67D8B75-ADCA-454A-90A2-7B3827ED99FF}"/>
     <hyperlink ref="O31" r:id="rId5" xr:uid="{2156ACCA-5D51-4A13-B679-1A5F84AF210C}"/>
-    <hyperlink ref="O47" r:id="rId6" xr:uid="{F4AF2DE2-2F5A-4F8F-AE3B-B74333079DBA}"/>
-    <hyperlink ref="O46" r:id="rId7" xr:uid="{E3681D50-BCF6-45BF-92E2-FA79AE9F7F63}"/>
-    <hyperlink ref="O33" r:id="rId8" xr:uid="{708B72BB-8155-435C-A98A-443BAD0793CE}"/>
-    <hyperlink ref="O42" r:id="rId9" xr:uid="{5A47B33C-2078-42A0-97CB-FDA2AEFAD03A}"/>
-    <hyperlink ref="O37" r:id="rId10" xr:uid="{69A12946-F47E-4DFE-985E-8D4693A7CC10}"/>
-    <hyperlink ref="O10" r:id="rId11" xr:uid="{8FDB36E3-3359-4086-A00B-9B44E30AE660}"/>
-    <hyperlink ref="O11" r:id="rId12" xr:uid="{3348A2EA-3BD0-47EE-8D96-64F7519EA682}"/>
-    <hyperlink ref="O13" r:id="rId13" xr:uid="{F6C212B2-15D4-464A-A620-9DC42777AB26}"/>
-    <hyperlink ref="O16" r:id="rId14" xr:uid="{6C5E3693-5C77-457F-8D07-198366E2398D}"/>
-    <hyperlink ref="O17" r:id="rId15" xr:uid="{53C23FF1-FE99-4B67-B6FF-04B3CB1B9110}"/>
-    <hyperlink ref="O19" r:id="rId16" xr:uid="{7B46B2C0-14AE-4B4E-805C-D393B1A50D70}"/>
-    <hyperlink ref="O12" r:id="rId17" xr:uid="{382FF0FA-7010-4BD6-B83E-B24898DEAFC2}"/>
-    <hyperlink ref="O20" r:id="rId18" xr:uid="{AE531983-D06C-4C60-B45D-E4544B04C394}"/>
-    <hyperlink ref="O21" r:id="rId19" xr:uid="{45297EE2-EE7D-4B4F-A3C8-9A5E031EF4B4}"/>
-    <hyperlink ref="O22" r:id="rId20" xr:uid="{0DAF9DCD-55F7-4DC6-A56C-F28831022179}"/>
-    <hyperlink ref="O23" r:id="rId21" xr:uid="{175B306F-E9B1-4F1E-AD1F-3E90011CB1AA}"/>
-    <hyperlink ref="O24" r:id="rId22" xr:uid="{1681AD64-2563-48EE-8A92-950CAE9B7331}"/>
-    <hyperlink ref="O27" r:id="rId23" xr:uid="{B770F765-5335-487F-9967-272DD1C9A2E1}"/>
-    <hyperlink ref="O34" r:id="rId24" xr:uid="{0D74FD7F-A6AB-421A-8F10-7C11981AF05F}"/>
-    <hyperlink ref="O35" r:id="rId25" xr:uid="{57959F40-302E-4C7E-BCCB-DC9E117DC9C9}"/>
-    <hyperlink ref="O36" r:id="rId26" xr:uid="{6D489768-7C07-4E89-B8C4-B27785A5ACC4}"/>
-    <hyperlink ref="O38" r:id="rId27" xr:uid="{421CEA32-ED48-4D99-ADE3-24AC8291EFF0}"/>
-    <hyperlink ref="O39" r:id="rId28" xr:uid="{8AD47C0D-DD20-446B-99FD-D1C94B901710}"/>
-    <hyperlink ref="O43" r:id="rId29" xr:uid="{39F5D6FC-B79E-4A23-A4F5-F94AE19CCF54}"/>
-    <hyperlink ref="O44" r:id="rId30" xr:uid="{26F56D36-5160-4F93-B0FE-BA5D7F279576}"/>
-    <hyperlink ref="O50" r:id="rId31" xr:uid="{0141DE74-1F28-4DA9-B73A-7BD298437E30}"/>
-    <hyperlink ref="O51" r:id="rId32" xr:uid="{71472283-ADCE-419D-B345-3F78D4C9B4A1}"/>
-    <hyperlink ref="O15" r:id="rId33" xr:uid="{386A98B2-E463-46C3-98CA-031EE3ACAF7E}"/>
-    <hyperlink ref="O18" r:id="rId34" xr:uid="{3F640406-EF82-415C-B941-ACDE17CD6FD1}"/>
-    <hyperlink ref="O41" r:id="rId35" xr:uid="{43DD3F14-DD7D-4C17-951A-197F63191CA8}"/>
+    <hyperlink ref="O46" r:id="rId6" xr:uid="{E3681D50-BCF6-45BF-92E2-FA79AE9F7F63}"/>
+    <hyperlink ref="O33" r:id="rId7" xr:uid="{708B72BB-8155-435C-A98A-443BAD0793CE}"/>
+    <hyperlink ref="O42" r:id="rId8" xr:uid="{5A47B33C-2078-42A0-97CB-FDA2AEFAD03A}"/>
+    <hyperlink ref="O37" r:id="rId9" xr:uid="{69A12946-F47E-4DFE-985E-8D4693A7CC10}"/>
+    <hyperlink ref="O10" r:id="rId10" xr:uid="{8FDB36E3-3359-4086-A00B-9B44E30AE660}"/>
+    <hyperlink ref="O11" r:id="rId11" xr:uid="{3348A2EA-3BD0-47EE-8D96-64F7519EA682}"/>
+    <hyperlink ref="O13" r:id="rId12" xr:uid="{F6C212B2-15D4-464A-A620-9DC42777AB26}"/>
+    <hyperlink ref="O16" r:id="rId13" xr:uid="{6C5E3693-5C77-457F-8D07-198366E2398D}"/>
+    <hyperlink ref="O17" r:id="rId14" xr:uid="{53C23FF1-FE99-4B67-B6FF-04B3CB1B9110}"/>
+    <hyperlink ref="O19" r:id="rId15" xr:uid="{7B46B2C0-14AE-4B4E-805C-D393B1A50D70}"/>
+    <hyperlink ref="O12" r:id="rId16" xr:uid="{382FF0FA-7010-4BD6-B83E-B24898DEAFC2}"/>
+    <hyperlink ref="O20" r:id="rId17" xr:uid="{AE531983-D06C-4C60-B45D-E4544B04C394}"/>
+    <hyperlink ref="O21" r:id="rId18" xr:uid="{45297EE2-EE7D-4B4F-A3C8-9A5E031EF4B4}"/>
+    <hyperlink ref="O22" r:id="rId19" xr:uid="{0DAF9DCD-55F7-4DC6-A56C-F28831022179}"/>
+    <hyperlink ref="O23" r:id="rId20" xr:uid="{175B306F-E9B1-4F1E-AD1F-3E90011CB1AA}"/>
+    <hyperlink ref="O24" r:id="rId21" xr:uid="{1681AD64-2563-48EE-8A92-950CAE9B7331}"/>
+    <hyperlink ref="O27" r:id="rId22" xr:uid="{B770F765-5335-487F-9967-272DD1C9A2E1}"/>
+    <hyperlink ref="O34" r:id="rId23" xr:uid="{0D74FD7F-A6AB-421A-8F10-7C11981AF05F}"/>
+    <hyperlink ref="O35" r:id="rId24" xr:uid="{57959F40-302E-4C7E-BCCB-DC9E117DC9C9}"/>
+    <hyperlink ref="O36" r:id="rId25" xr:uid="{6D489768-7C07-4E89-B8C4-B27785A5ACC4}"/>
+    <hyperlink ref="O38" r:id="rId26" xr:uid="{421CEA32-ED48-4D99-ADE3-24AC8291EFF0}"/>
+    <hyperlink ref="O39" r:id="rId27" xr:uid="{8AD47C0D-DD20-446B-99FD-D1C94B901710}"/>
+    <hyperlink ref="O43" r:id="rId28" xr:uid="{39F5D6FC-B79E-4A23-A4F5-F94AE19CCF54}"/>
+    <hyperlink ref="O44" r:id="rId29" xr:uid="{26F56D36-5160-4F93-B0FE-BA5D7F279576}"/>
+    <hyperlink ref="O50" r:id="rId30" xr:uid="{0141DE74-1F28-4DA9-B73A-7BD298437E30}"/>
+    <hyperlink ref="O51" r:id="rId31" xr:uid="{71472283-ADCE-419D-B345-3F78D4C9B4A1}"/>
+    <hyperlink ref="O15" r:id="rId32" xr:uid="{386A98B2-E463-46C3-98CA-031EE3ACAF7E}"/>
+    <hyperlink ref="O18" r:id="rId33" xr:uid="{3F640406-EF82-415C-B941-ACDE17CD6FD1}"/>
+    <hyperlink ref="O41" r:id="rId34" xr:uid="{43DD3F14-DD7D-4C17-951A-197F63191CA8}"/>
+    <hyperlink ref="O47" r:id="rId35" xr:uid="{E0D66AE9-7350-447C-A855-132FBE78F6D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
@@ -4920,7 +4932,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -4945,7 +4957,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -4970,7 +4982,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -5110,19 +5122,19 @@
         <v>204</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="N9" s="31" t="s">
         <v>260</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>261</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>216</v>
       </c>
       <c r="P9" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>262</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>263</v>
       </c>
       <c r="R9" s="31" t="s">
         <v>219</v>
@@ -5215,7 +5227,7 @@
         <v>229</v>
       </c>
       <c r="J11" s="45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K11" s="58" t="s">
         <v>186</v>
@@ -5253,7 +5265,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" s="67" t="s">
         <v>61</v>
@@ -5327,7 +5339,7 @@
         <v>229</v>
       </c>
       <c r="J13" s="45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K13" s="58" t="s">
         <v>188</v>
@@ -5421,7 +5433,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E15" s="45" t="s">
         <v>56</v>
@@ -5436,10 +5448,10 @@
         <v>155</v>
       </c>
       <c r="I15" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="J15" s="45" t="s">
         <v>268</v>
-      </c>
-      <c r="J15" s="45" t="s">
-        <v>269</v>
       </c>
       <c r="K15" s="58" t="s">
         <v>190</v>
@@ -5495,7 +5507,7 @@
         <v>229</v>
       </c>
       <c r="J16" s="61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K16" s="68" t="s">
         <v>191</v>
@@ -5551,7 +5563,7 @@
         <v>229</v>
       </c>
       <c r="J17" s="78" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K17" s="80" t="s">
         <v>192</v>
@@ -5589,7 +5601,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E18" s="67" t="s">
         <v>59</v>
@@ -5604,10 +5616,10 @@
         <v>159</v>
       </c>
       <c r="I18" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="J18" s="61" t="s">
         <v>270</v>
-      </c>
-      <c r="J18" s="61" t="s">
-        <v>271</v>
       </c>
       <c r="K18" s="68" t="s">
         <v>193</v>
@@ -5719,7 +5731,7 @@
         <v>229</v>
       </c>
       <c r="J20" s="61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K20" s="68" t="s">
         <v>195</v>
@@ -5887,7 +5899,7 @@
         <v>229</v>
       </c>
       <c r="J23" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K23" s="80" t="s">
         <v>193</v>
@@ -6305,7 +6317,7 @@
         <v>4090.5</v>
       </c>
       <c r="R30" s="95" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S30" s="70"/>
     </row>
@@ -6418,7 +6430,7 @@
         <v>229</v>
       </c>
       <c r="R32" s="74" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S32" s="94"/>
     </row>
@@ -6447,10 +6459,10 @@
         <v>162</v>
       </c>
       <c r="I33" s="78" t="s">
+        <v>242</v>
+      </c>
+      <c r="J33" s="78" t="s">
         <v>243</v>
-      </c>
-      <c r="J33" s="78" t="s">
-        <v>244</v>
       </c>
       <c r="K33" s="80" t="s">
         <v>197</v>
@@ -6506,7 +6518,7 @@
         <v>229</v>
       </c>
       <c r="J34" s="66" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K34" s="86" t="s">
         <v>198</v>
@@ -6562,7 +6574,7 @@
         <v>229</v>
       </c>
       <c r="J35" s="45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K35" s="58" t="s">
         <v>199</v>
@@ -6672,7 +6684,7 @@
       </c>
       <c r="I37" s="45"/>
       <c r="J37" s="45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K37" s="58" t="s">
         <v>201</v>
@@ -6710,7 +6722,7 @@
         <v>208</v>
       </c>
       <c r="D38" s="71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E38" s="67" t="s">
         <v>80</v>
@@ -6784,7 +6796,7 @@
         <v>229</v>
       </c>
       <c r="J39" s="45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K39" s="58" t="s">
         <v>203</v>
@@ -6865,7 +6877,7 @@
         <v>229</v>
       </c>
       <c r="R40" s="74" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="S40" s="94"/>
     </row>
@@ -6923,7 +6935,7 @@
         <v>39.9</v>
       </c>
       <c r="R41" s="89" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S41" s="47"/>
     </row>
@@ -6981,7 +6993,7 @@
         <v>3366</v>
       </c>
       <c r="R42" s="95" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S42" s="70"/>
     </row>
@@ -7039,7 +7051,7 @@
         <v>17692.12</v>
       </c>
       <c r="R43" s="96" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S43" s="47"/>
     </row>
@@ -7071,7 +7083,7 @@
         <v>229</v>
       </c>
       <c r="J44" s="61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>229</v>
@@ -7153,7 +7165,7 @@
         <v>8466</v>
       </c>
       <c r="R45" s="89" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S45" s="47"/>
     </row>
@@ -7173,7 +7185,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="61" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G46" s="67" t="s">
         <v>118</v>
@@ -7229,7 +7241,7 @@
         <v>89</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G47" s="46" t="s">
         <v>119</v>
@@ -7267,7 +7279,7 @@
         <v>93.84</v>
       </c>
       <c r="R47" s="89" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S47" s="47"/>
     </row>
@@ -7325,7 +7337,7 @@
         <v>4896</v>
       </c>
       <c r="R48" s="95" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S48" s="70"/>
     </row>
@@ -7383,7 +7395,7 @@
         <v>7638</v>
       </c>
       <c r="R49" s="96" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S49" s="47"/>
     </row>
@@ -7415,10 +7427,10 @@
         <v>229</v>
       </c>
       <c r="J50" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="K50" s="68" t="s">
         <v>239</v>
-      </c>
-      <c r="K50" s="68" t="s">
-        <v>240</v>
       </c>
       <c r="L50" s="61">
         <v>1</v>
@@ -7471,10 +7483,10 @@
         <v>229</v>
       </c>
       <c r="J51" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="K51" s="58" t="s">
         <v>241</v>
-      </c>
-      <c r="K51" s="58" t="s">
-        <v>242</v>
       </c>
       <c r="L51" s="75">
         <v>2</v>
@@ -7819,7 +7831,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -7844,7 +7856,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -7869,7 +7881,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -8114,7 +8126,7 @@
         <v>229</v>
       </c>
       <c r="J11" s="45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K11" s="58" t="s">
         <v>186</v>
@@ -8152,7 +8164,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" s="67" t="s">
         <v>61</v>
@@ -8226,7 +8238,7 @@
         <v>229</v>
       </c>
       <c r="J13" s="45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K13" s="58" t="s">
         <v>188</v>
@@ -8320,7 +8332,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E15" s="45" t="s">
         <v>56</v>
@@ -8335,10 +8347,10 @@
         <v>155</v>
       </c>
       <c r="I15" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="J15" s="45" t="s">
         <v>268</v>
-      </c>
-      <c r="J15" s="45" t="s">
-        <v>269</v>
       </c>
       <c r="K15" s="58" t="s">
         <v>190</v>
@@ -8394,7 +8406,7 @@
         <v>229</v>
       </c>
       <c r="J16" s="61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K16" s="68" t="s">
         <v>191</v>
@@ -8450,7 +8462,7 @@
         <v>229</v>
       </c>
       <c r="J17" s="78" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K17" s="80" t="s">
         <v>192</v>
@@ -8488,7 +8500,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E18" s="67" t="s">
         <v>59</v>
@@ -8503,10 +8515,10 @@
         <v>159</v>
       </c>
       <c r="I18" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="J18" s="61" t="s">
         <v>270</v>
-      </c>
-      <c r="J18" s="61" t="s">
-        <v>271</v>
       </c>
       <c r="K18" s="68" t="s">
         <v>193</v>
@@ -8618,7 +8630,7 @@
         <v>229</v>
       </c>
       <c r="J20" s="61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K20" s="68" t="s">
         <v>195</v>
@@ -8786,7 +8798,7 @@
         <v>229</v>
       </c>
       <c r="J23" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K23" s="80" t="s">
         <v>193</v>
@@ -9148,7 +9160,7 @@
         <v>28872</v>
       </c>
       <c r="R29" s="89" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S29" s="47"/>
     </row>
@@ -9206,7 +9218,7 @@
         <v>20100</v>
       </c>
       <c r="R30" s="97" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="S30" s="70"/>
     </row>
@@ -9342,10 +9354,10 @@
         <v>162</v>
       </c>
       <c r="I33" s="78" t="s">
+        <v>242</v>
+      </c>
+      <c r="J33" s="78" t="s">
         <v>243</v>
-      </c>
-      <c r="J33" s="78" t="s">
-        <v>244</v>
       </c>
       <c r="K33" s="80" t="s">
         <v>197</v>
@@ -9401,7 +9413,7 @@
         <v>229</v>
       </c>
       <c r="J34" s="66" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K34" s="86" t="s">
         <v>198</v>
@@ -9457,7 +9469,7 @@
         <v>229</v>
       </c>
       <c r="J35" s="45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K35" s="58" t="s">
         <v>199</v>
@@ -9567,7 +9579,7 @@
       </c>
       <c r="I37" s="45"/>
       <c r="J37" s="45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K37" s="58" t="s">
         <v>201</v>
@@ -9605,7 +9617,7 @@
         <v>208</v>
       </c>
       <c r="D38" s="71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E38" s="67" t="s">
         <v>80</v>
@@ -9679,7 +9691,7 @@
         <v>229</v>
       </c>
       <c r="J39" s="45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K39" s="58" t="s">
         <v>203</v>
@@ -9812,7 +9824,7 @@
         <v>111.1</v>
       </c>
       <c r="R41" s="89" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S41" s="47"/>
     </row>
@@ -9870,7 +9882,7 @@
         <v>15662.4</v>
       </c>
       <c r="R42" s="95" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S42" s="70"/>
     </row>
@@ -9928,7 +9940,7 @@
         <v>88460.599999999991</v>
       </c>
       <c r="R43" s="96" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="S43" s="47"/>
     </row>
@@ -9960,7 +9972,7 @@
         <v>229</v>
       </c>
       <c r="J44" s="61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K44" s="68" t="s">
         <v>229</v>
@@ -10060,7 +10072,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="61" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G46" s="67" t="s">
         <v>118</v>
@@ -10116,7 +10128,7 @@
         <v>89</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G47" s="46" t="s">
         <v>119</v>
@@ -10210,7 +10222,7 @@
         <v>16982.66</v>
       </c>
       <c r="R48" s="97" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="S48" s="70"/>
     </row>
@@ -10268,7 +10280,7 @@
         <v>25363.249999999996</v>
       </c>
       <c r="R49" s="96" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="S49" s="47"/>
     </row>
@@ -10300,10 +10312,10 @@
         <v>229</v>
       </c>
       <c r="J50" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="K50" s="68" t="s">
         <v>239</v>
-      </c>
-      <c r="K50" s="68" t="s">
-        <v>240</v>
       </c>
       <c r="L50" s="61">
         <v>1</v>
@@ -10356,10 +10368,10 @@
         <v>229</v>
       </c>
       <c r="J51" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="K51" s="58" t="s">
         <v>241</v>
-      </c>
-      <c r="K51" s="58" t="s">
-        <v>242</v>
       </c>
       <c r="L51" s="75">
         <v>2</v>

--- a/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07670EB1-03E7-4C59-8C4B-9D4D8AC67800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10616AFF-8CD5-4EE6-9A27-304F451BBA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="296">
   <si>
     <t>Component list</t>
   </si>
@@ -892,6 +892,39 @@
   </si>
   <si>
     <t>RS-03K104JT</t>
+  </si>
+  <si>
+    <t>C3, C5, C7, C9, C11, C13, C15, C17, C24, C25, C27, C29, C30, C32, C35, C39, C42, C53, C55, C64, C65, C66, C67, C70, C72, C76, C78, C85, C90, C91, C92, C93, C94, C95, C98, C99, C108, C112, C113, C114, C116, C118, C120, C128, C135, C136, C165, C166, C167, C168, C#2</t>
+  </si>
+  <si>
+    <t>C45, C46, C47, C48, C49, C50, C51, C52, C97, C100, C101, C102, C103, C104, C105, C106, C107, C119, C122, C123, C126, C130, C133, C134, C141, C142, C143, C144, C145, C146, C147, C148, C149, C150, C151, C152, C153, C154, C155, C156, C157, C158, C159, C160, C161, C162, C163, C164</t>
+  </si>
+  <si>
+    <t>C2168289</t>
+  </si>
+  <si>
+    <t>Ferrite Bead</t>
+  </si>
+  <si>
+    <t>FB1, FB2</t>
+  </si>
+  <si>
+    <t>FERRITE BEAD 120 OHM 0603 1LN</t>
+  </si>
+  <si>
+    <t>IND-0603 (1608 Metric)</t>
+  </si>
+  <si>
+    <t>BLM18SG121TN1D</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>C113030</t>
+  </si>
+  <si>
+    <t>C1,C2, C23, C26, C28, C137, C138, C139, C140</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1713,6 +1746,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2218,7 +2266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C605574B-18B4-4F8A-BF86-58CC88FF11BE}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -2482,7 +2530,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="63"/>
       <c r="B10" s="37">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2492,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="E10" s="67" t="s">
         <v>51</v>
@@ -2516,14 +2564,14 @@
         <v>181</v>
       </c>
       <c r="L10" s="61">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M10" s="61">
         <f>L10*5</f>
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="N10" s="61">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="O10" s="69" t="s">
         <v>223</v>
@@ -2533,87 +2581,87 @@
       </c>
       <c r="Q10" s="70">
         <f>P10*N10</f>
-        <v>2.8319999999999999</v>
+        <v>1.4159999999999999</v>
       </c>
       <c r="R10" s="67"/>
       <c r="S10" s="70"/>
     </row>
-    <row r="11" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" s="64" customFormat="1" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="63"/>
       <c r="B11" s="37">
-        <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="I11" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J11" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="K11" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="L11" s="59">
-        <v>1</v>
-      </c>
-      <c r="M11" s="59">
-        <f t="shared" ref="M11:M50" si="1">L11*5</f>
-        <v>5</v>
-      </c>
-      <c r="N11" s="45">
-        <v>20</v>
-      </c>
-      <c r="O11" s="62" t="s">
+      <c r="D11" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="K11" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="L11" s="61">
+        <v>51</v>
+      </c>
+      <c r="M11" s="61">
+        <f t="shared" ref="M11:M49" si="0">L11*5</f>
+        <v>255</v>
+      </c>
+      <c r="N11" s="61">
+        <v>300</v>
+      </c>
+      <c r="O11" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P11" s="47">
-        <v>1.7399999999999999E-2</v>
-      </c>
-      <c r="Q11" s="47">
-        <f t="shared" ref="Q11:Q50" si="2">P11*N11</f>
-        <v>0.34799999999999998</v>
-      </c>
-      <c r="R11" s="46"/>
-      <c r="S11" s="47"/>
-    </row>
-    <row r="12" spans="1:19" s="64" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P11" s="70">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q11" s="70">
+        <f>P11*N11</f>
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="R11" s="67"/>
+      <c r="S11" s="70"/>
+    </row>
+    <row r="12" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="63"/>
       <c r="B12" s="37">
-        <f>ROW(B12) - ROW($B$9)</f>
+        <f t="shared" ref="B12:B48" si="1">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="E12" s="67" t="s">
-        <v>60</v>
+      <c r="D12" s="110" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>53</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G12" s="67" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H12" s="61" t="s">
         <v>152</v>
@@ -2622,91 +2670,91 @@
         <v>225</v>
       </c>
       <c r="J12" s="61" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="K12" s="68" t="s">
-        <v>183</v>
-      </c>
-      <c r="L12" s="61">
-        <v>43</v>
-      </c>
-      <c r="M12" s="61">
-        <f t="shared" si="1"/>
-        <v>215</v>
+        <v>184</v>
+      </c>
+      <c r="L12" s="111">
+        <v>12</v>
+      </c>
+      <c r="M12" s="111">
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="N12" s="61">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="O12" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P12" s="70">
-        <v>8.9999999999999993E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="Q12" s="70">
-        <f>P12*N12</f>
-        <v>2.25</v>
+        <f t="shared" ref="Q12:Q49" si="2">P12*N12</f>
+        <v>0.27999999999999997</v>
       </c>
       <c r="R12" s="67"/>
       <c r="S12" s="70"/>
     </row>
-    <row r="13" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="63"/>
       <c r="B13" s="37">
+        <f>ROW(B13) - ROW($B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="K13" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="L13" s="61">
+        <v>2</v>
+      </c>
+      <c r="M13" s="61">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J13" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="K13" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="L13" s="59">
-        <v>12</v>
-      </c>
-      <c r="M13" s="59">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N13" s="45">
-        <v>100</v>
-      </c>
-      <c r="O13" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="N13" s="61">
+        <v>11</v>
+      </c>
+      <c r="O13" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P13" s="47">
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q13" s="47">
+      <c r="P13" s="70">
+        <v>1.2005999999999999</v>
+      </c>
+      <c r="Q13" s="70">
         <f t="shared" si="2"/>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="R13" s="46"/>
-      <c r="S13" s="47"/>
-    </row>
-    <row r="14" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13.206599999999998</v>
+      </c>
+      <c r="R13" s="67"/>
+      <c r="S13" s="70"/>
+    </row>
+    <row r="14" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="63"/>
       <c r="B14" s="37">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2715,220 +2763,220 @@
       <c r="C14" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="110" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>262</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>263</v>
+      </c>
+      <c r="K14" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="L14" s="111">
         <v>16</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="67" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="I14" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="J14" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="K14" s="68" t="s">
-        <v>185</v>
-      </c>
-      <c r="L14" s="61">
-        <v>2</v>
-      </c>
-      <c r="M14" s="61">
-        <f t="shared" si="1"/>
-        <v>10</v>
+      <c r="M14" s="111">
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
       <c r="N14" s="61">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="O14" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P14" s="70">
-        <v>1.2005999999999999</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q14" s="70">
         <f t="shared" si="2"/>
-        <v>13.206599999999998</v>
+        <v>0.25</v>
       </c>
       <c r="R14" s="67"/>
       <c r="S14" s="70"/>
     </row>
-    <row r="15" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="63"/>
       <c r="B15" s="37">
-        <f>ROW(B15) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="72" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I15" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="J15" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="K15" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="L15" s="59">
-        <v>16</v>
-      </c>
-      <c r="M15" s="59">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N15" s="45">
-        <v>100</v>
-      </c>
-      <c r="O15" s="62" t="s">
+      <c r="D15" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>246</v>
+      </c>
+      <c r="K15" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N15" s="61">
+        <v>10</v>
+      </c>
+      <c r="O15" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P15" s="47">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="Q15" s="47">
+      <c r="P15" s="70">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="Q15" s="70">
         <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="R15" s="46"/>
-      <c r="S15" s="47"/>
-    </row>
-    <row r="16" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.377</v>
+      </c>
+      <c r="R15" s="67"/>
+      <c r="S15" s="70"/>
+    </row>
+    <row r="16" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="63"/>
       <c r="B16" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="71" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="67" t="s">
-        <v>56</v>
+      <c r="D16" s="110" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>57</v>
       </c>
       <c r="F16" s="61" t="s">
         <v>94</v>
       </c>
       <c r="G16" s="67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H16" s="61" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I16" s="61" t="s">
         <v>225</v>
       </c>
       <c r="J16" s="61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K16" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="L16" s="61">
-        <v>1</v>
-      </c>
-      <c r="M16" s="61">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>188</v>
+      </c>
+      <c r="L16" s="111">
+        <v>6</v>
+      </c>
+      <c r="M16" s="111">
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="N16" s="61">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O16" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P16" s="70">
-        <v>3.7699999999999997E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q16" s="70">
         <f t="shared" si="2"/>
-        <v>0.377</v>
+        <v>0.27</v>
       </c>
       <c r="R16" s="67"/>
       <c r="S16" s="70"/>
     </row>
-    <row r="17" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" s="64" customFormat="1" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="63"/>
       <c r="B17" s="37">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="45" t="s">
+      <c r="D17" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="I17" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J17" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="K17" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="L17" s="59">
-        <v>6</v>
-      </c>
-      <c r="M17" s="59">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N17" s="45">
-        <v>100</v>
-      </c>
-      <c r="O17" s="62" t="s">
+      <c r="I17" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J17" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="L17" s="61">
+        <v>48</v>
+      </c>
+      <c r="M17" s="61">
+        <f>L17*5</f>
+        <v>240</v>
+      </c>
+      <c r="N17" s="61">
+        <v>300</v>
+      </c>
+      <c r="O17" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P17" s="47">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="Q17" s="47">
-        <f t="shared" si="2"/>
-        <v>0.27</v>
-      </c>
-      <c r="R17" s="46"/>
-      <c r="S17" s="47"/>
+      <c r="P17" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q17" s="70">
+        <f>P17*N17</f>
+        <v>0.33</v>
+      </c>
+      <c r="R17" s="67"/>
+      <c r="S17" s="70"/>
     </row>
     <row r="18" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="63"/>
@@ -2939,7 +2987,7 @@
       <c r="C18" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="110" t="s">
         <v>277</v>
       </c>
       <c r="E18" s="67" t="s">
@@ -2948,17 +2996,17 @@
       <c r="F18" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="74" t="s">
-        <v>134</v>
+      <c r="G18" s="61" t="s">
+        <v>264</v>
       </c>
       <c r="H18" s="61" t="s">
         <v>156</v>
       </c>
       <c r="I18" s="61" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="J18" s="61" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="K18" s="68" t="s">
         <v>189</v>
@@ -2967,7 +3015,7 @@
         <v>11</v>
       </c>
       <c r="M18" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="N18" s="61">
@@ -2992,60 +3040,60 @@
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="I19" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J19" s="45" t="s">
+      <c r="I19" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J19" s="61" t="s">
         <v>172</v>
       </c>
-      <c r="K19" s="58" t="s">
+      <c r="K19" s="68" t="s">
         <v>190</v>
       </c>
-      <c r="L19" s="59">
+      <c r="L19" s="111">
         <v>4</v>
       </c>
-      <c r="M19" s="59">
-        <f t="shared" si="1"/>
+      <c r="M19" s="111">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N19" s="45">
+      <c r="N19" s="61">
         <v>100</v>
       </c>
-      <c r="O19" s="62" t="s">
+      <c r="O19" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P19" s="47">
+      <c r="P19" s="70">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q19" s="47">
+      <c r="Q19" s="70">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
-      <c r="R19" s="46"/>
-      <c r="S19" s="47"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="70"/>
     </row>
     <row r="20" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="63"/>
       <c r="B20" s="37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="C20" s="53" t="s">
@@ -3079,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N20" s="61">
@@ -3104,108 +3152,108 @@
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="45" t="s">
+      <c r="F21" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="I21" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J21" s="45" t="s">
+      <c r="I21" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J21" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="K21" s="68" t="s">
         <v>192</v>
       </c>
-      <c r="L21" s="59">
+      <c r="L21" s="111">
         <v>8</v>
       </c>
-      <c r="M21" s="59">
-        <f t="shared" si="1"/>
+      <c r="M21" s="111">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="N21" s="45">
+      <c r="N21" s="61">
         <v>100</v>
       </c>
-      <c r="O21" s="62" t="s">
+      <c r="O21" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P21" s="47">
+      <c r="P21" s="70">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="Q21" s="47">
+      <c r="Q21" s="70">
         <f t="shared" si="2"/>
         <v>0.27</v>
       </c>
-      <c r="R21" s="46"/>
-      <c r="S21" s="47"/>
-    </row>
-    <row r="22" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="67"/>
+      <c r="S21" s="70"/>
+    </row>
+    <row r="22" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="63"/>
       <c r="B22" s="37">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="67" t="s">
-        <v>63</v>
+        <v>201</v>
+      </c>
+      <c r="D22" s="110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="61" t="s">
+        <v>65</v>
       </c>
       <c r="F22" s="61" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="G22" s="67" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="H22" s="61" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I22" s="61" t="s">
         <v>225</v>
       </c>
       <c r="J22" s="61" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="K22" s="68" t="s">
-        <v>186</v>
-      </c>
-      <c r="L22" s="61">
-        <v>8</v>
-      </c>
-      <c r="M22" s="61">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <v>225</v>
+      </c>
+      <c r="L22" s="111">
+        <v>1</v>
+      </c>
+      <c r="M22" s="111">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="N22" s="61">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O22" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P22" s="70">
-        <v>1.1000000000000001E-3</v>
+        <v>3.9800000000000002E-2</v>
       </c>
       <c r="Q22" s="70">
         <f t="shared" si="2"/>
-        <v>0.11</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="R22" s="67"/>
       <c r="S22" s="70"/>
@@ -3213,582 +3261,581 @@
     <row r="23" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="63"/>
       <c r="B23" s="37">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="K23" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L23" s="61">
+        <v>1</v>
+      </c>
+      <c r="M23" s="61">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="G23" s="46" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="I23" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J23" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="K23" s="58" t="s">
-        <v>189</v>
-      </c>
-      <c r="L23" s="59">
-        <v>8</v>
-      </c>
-      <c r="M23" s="59">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N23" s="45">
-        <v>45</v>
-      </c>
-      <c r="O23" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="61">
+        <v>10</v>
+      </c>
+      <c r="O23" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P23" s="47">
-        <v>8.9399999999999993E-2</v>
-      </c>
-      <c r="Q23" s="47">
+      <c r="P23" s="70">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="Q23" s="70">
         <f t="shared" si="2"/>
-        <v>4.0229999999999997</v>
-      </c>
-      <c r="R23" s="46"/>
-      <c r="S23" s="47"/>
-    </row>
-    <row r="24" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.318</v>
+      </c>
+      <c r="R23" s="67"/>
+      <c r="S23" s="70"/>
+    </row>
+    <row r="24" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="63"/>
       <c r="B24" s="37">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="D24" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="I24" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J24" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="K24" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L24" s="59">
-        <v>1</v>
-      </c>
-      <c r="M24" s="59">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N24" s="45">
+      <c r="C24" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="D24" s="109" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="109" t="s">
+        <v>290</v>
+      </c>
+      <c r="F24" s="109" t="s">
+        <v>291</v>
+      </c>
+      <c r="G24" s="109" t="s">
+        <v>292</v>
+      </c>
+      <c r="H24" s="109" t="s">
+        <v>293</v>
+      </c>
+      <c r="I24" s="109" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24" s="109" t="s">
+        <v>294</v>
+      </c>
+      <c r="K24" s="109" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="109">
+        <v>2</v>
+      </c>
+      <c r="M24" s="111">
+        <f>L24*5</f>
         <v>10</v>
       </c>
-      <c r="O24" s="62" t="s">
+      <c r="N24" s="61">
+        <v>20</v>
+      </c>
+      <c r="O24" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P24" s="47">
-        <v>3.9800000000000002E-2</v>
-      </c>
-      <c r="Q24" s="47">
-        <f t="shared" si="2"/>
-        <v>0.39800000000000002</v>
-      </c>
-      <c r="R24" s="46"/>
-      <c r="S24" s="47"/>
-    </row>
-    <row r="25" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P24" s="70">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q24" s="70">
+        <f>P24*N24</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R24" s="67"/>
+      <c r="S24" s="70"/>
+    </row>
+    <row r="25" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="63"/>
       <c r="B25" s="37">
-        <f>ROW(B25) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="D25" s="71" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="67" t="s">
-        <v>66</v>
+        <v>202</v>
+      </c>
+      <c r="D25" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="61" t="s">
+        <v>67</v>
       </c>
       <c r="F25" s="61" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25" s="67" t="s">
-        <v>137</v>
+        <v>101</v>
+      </c>
+      <c r="G25" s="74" t="s">
+        <v>138</v>
       </c>
       <c r="H25" s="61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I25" s="61" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J25" s="61" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K25" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L25" s="61">
+      <c r="L25" s="111">
         <v>1</v>
       </c>
-      <c r="M25" s="61">
-        <f t="shared" si="1"/>
+      <c r="M25" s="111">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N25" s="61">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O25" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P25" s="70">
-        <v>3.1800000000000002E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="Q25" s="70">
         <f t="shared" si="2"/>
-        <v>0.318</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="R25" s="67"/>
       <c r="S25" s="70"/>
     </row>
-    <row r="26" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="63"/>
       <c r="B26" s="37">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L26" s="61">
+        <v>1</v>
+      </c>
+      <c r="M26" s="61">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="73" t="s">
-        <v>138</v>
-      </c>
-      <c r="H26" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="45" t="s">
-        <v>228</v>
-      </c>
-      <c r="J26" s="45" t="s">
-        <v>229</v>
-      </c>
-      <c r="K26" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L26" s="59">
-        <v>1</v>
-      </c>
-      <c r="M26" s="59">
-        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N26" s="45">
-        <v>20</v>
-      </c>
-      <c r="O26" s="62" t="s">
+      <c r="N26" s="61">
+        <v>10</v>
+      </c>
+      <c r="O26" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P26" s="47">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="Q26" s="47">
+      <c r="P26" s="70">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="Q26" s="70">
         <f t="shared" si="2"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="R26" s="46"/>
-      <c r="S26" s="47"/>
-    </row>
-    <row r="27" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.55599999999999994</v>
+      </c>
+      <c r="R26" s="67"/>
+      <c r="S26" s="70"/>
+    </row>
+    <row r="27" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="63"/>
       <c r="B27" s="37">
-        <f>ROW(B27) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="67" t="s">
-        <v>68</v>
+        <v>9</v>
+      </c>
+      <c r="D27" s="110" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>69</v>
       </c>
       <c r="F27" s="61" t="s">
         <v>230</v>
       </c>
       <c r="G27" s="67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I27" s="61" t="s">
         <v>225</v>
       </c>
       <c r="J27" s="61" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="K27" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L27" s="61">
-        <v>1</v>
-      </c>
-      <c r="M27" s="61">
-        <f t="shared" si="1"/>
-        <v>5</v>
+      <c r="L27" s="111">
+        <v>8</v>
+      </c>
+      <c r="M27" s="111">
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="N27" s="61">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="O27" s="69" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="P27" s="70">
-        <v>5.5599999999999997E-2</v>
+        <v>0.84699999999999998</v>
       </c>
       <c r="Q27" s="70">
         <f t="shared" si="2"/>
-        <v>0.55599999999999994</v>
-      </c>
-      <c r="R27" s="67"/>
+        <v>38.115000000000002</v>
+      </c>
+      <c r="R27" s="95"/>
       <c r="S27" s="70"/>
     </row>
     <row r="28" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="63"/>
       <c r="B28" s="37">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K28" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L28" s="61">
+        <v>4</v>
+      </c>
+      <c r="M28" s="61">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="H28" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="I28" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J28" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K28" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L28" s="59">
-        <v>8</v>
-      </c>
-      <c r="M28" s="59">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N28" s="45">
-        <v>45</v>
-      </c>
-      <c r="O28" s="62" t="s">
-        <v>276</v>
-      </c>
-      <c r="P28" s="47">
-        <v>0.84699999999999998</v>
-      </c>
-      <c r="Q28" s="47">
+        <v>20</v>
+      </c>
+      <c r="N28" s="61">
+        <v>25</v>
+      </c>
+      <c r="O28" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P28" s="70">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="70">
         <f t="shared" si="2"/>
-        <v>38.115000000000002</v>
-      </c>
-      <c r="R28" s="89"/>
-      <c r="S28" s="47"/>
-    </row>
-    <row r="29" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="R28" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="S28" s="70"/>
+    </row>
+    <row r="29" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="63"/>
       <c r="B29" s="37">
-        <f>ROW(B29) - ROW($B$9)</f>
-        <v>20</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="71" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="67" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="G29" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="I29" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="J29" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="K29" s="68" t="s">
-        <v>225</v>
-      </c>
-      <c r="L29" s="61">
-        <v>4</v>
-      </c>
-      <c r="M29" s="61">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
+      <c r="C29" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="110" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="74">
+        <v>61300611121</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="J29" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="K29" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L29" s="111">
+        <v>1</v>
+      </c>
+      <c r="M29" s="111">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="N29" s="61">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O29" s="69" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="P29" s="70">
-        <v>2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="Q29" s="70">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R29" s="95" t="s">
-        <v>269</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="R29" s="67"/>
       <c r="S29" s="70"/>
     </row>
-    <row r="30" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="63"/>
       <c r="B30" s="37">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="I30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="J30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="K30" s="92" t="s">
+        <v>225</v>
+      </c>
+      <c r="L30" s="91">
+        <v>5</v>
+      </c>
+      <c r="M30" s="91">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" s="73">
-        <v>61300611121</v>
-      </c>
-      <c r="H30" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="J30" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="K30" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L30" s="59">
-        <v>1</v>
-      </c>
-      <c r="M30" s="59">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N30" s="45">
-        <v>20</v>
-      </c>
-      <c r="O30" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="P30" s="47">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="Q30" s="47">
-        <f t="shared" si="2"/>
-        <v>0.66</v>
-      </c>
-      <c r="R30" s="46"/>
-      <c r="S30" s="47"/>
+        <v>25</v>
+      </c>
+      <c r="N30" s="91"/>
+      <c r="O30" s="93" t="s">
+        <v>225</v>
+      </c>
+      <c r="P30" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q30" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="R30" s="74"/>
+      <c r="S30" s="94"/>
     </row>
     <row r="31" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="63"/>
       <c r="B31" s="37">
-        <f>ROW(B31) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="90" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="91" t="s">
-        <v>230</v>
+        <v>204</v>
+      </c>
+      <c r="D31" s="110" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="61" t="s">
+        <v>107</v>
       </c>
       <c r="G31" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="H31" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="I31" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="J31" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="K31" s="92" t="s">
-        <v>225</v>
-      </c>
-      <c r="L31" s="91">
-        <v>5</v>
-      </c>
-      <c r="M31" s="91">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="N31" s="91"/>
-      <c r="O31" s="93" t="s">
-        <v>225</v>
-      </c>
-      <c r="P31" s="94" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q31" s="94" t="s">
-        <v>225</v>
-      </c>
-      <c r="R31" s="74"/>
-      <c r="S31" s="94"/>
+        <v>139</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="J31" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="K31" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="L31" s="111">
+        <v>3</v>
+      </c>
+      <c r="M31" s="111">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="N31" s="61">
+        <v>100</v>
+      </c>
+      <c r="O31" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P31" s="70">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q31" s="70">
+        <f t="shared" si="2"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R31" s="67"/>
+      <c r="S31" s="70"/>
     </row>
     <row r="32" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="63"/>
       <c r="B32" s="37">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>250</v>
+      </c>
+      <c r="K32" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="L32" s="61">
+        <v>8</v>
+      </c>
+      <c r="M32" s="61">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="D32" s="72" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" s="73" t="s">
-        <v>139</v>
-      </c>
-      <c r="H32" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="I32" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="J32" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="K32" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="L32" s="59">
-        <v>3</v>
-      </c>
-      <c r="M32" s="59">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="N32" s="45">
+        <v>40</v>
+      </c>
+      <c r="N32" s="61">
         <v>100</v>
       </c>
-      <c r="O32" s="62" t="s">
+      <c r="O32" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P32" s="47">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q32" s="47">
+      <c r="P32" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q32" s="70">
         <f t="shared" si="2"/>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R32" s="46"/>
-      <c r="S32" s="47"/>
+        <v>0.11</v>
+      </c>
+      <c r="R32" s="67"/>
+      <c r="S32" s="70"/>
     </row>
     <row r="33" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="63"/>
       <c r="B33" s="37">
-        <f>ROW(B33) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="C33" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D33" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="67" t="s">
-        <v>74</v>
+      <c r="D33" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="61" t="s">
+        <v>75</v>
       </c>
       <c r="F33" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G33" s="67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H33" s="61" t="s">
         <v>152</v>
@@ -3797,17 +3844,17 @@
         <v>225</v>
       </c>
       <c r="J33" s="61" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="K33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="L33" s="61">
-        <v>8</v>
-      </c>
-      <c r="M33" s="61">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <v>195</v>
+      </c>
+      <c r="L33" s="111">
+        <v>3</v>
+      </c>
+      <c r="M33" s="111">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="N33" s="61">
         <v>100</v>
@@ -3816,91 +3863,91 @@
         <v>223</v>
       </c>
       <c r="P33" s="70">
-        <v>1.1000000000000001E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q33" s="70">
         <f t="shared" si="2"/>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="R33" s="67"/>
       <c r="S33" s="70"/>
     </row>
-    <row r="34" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="63"/>
       <c r="B34" s="37">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="L34" s="61">
+        <v>10</v>
+      </c>
+      <c r="M34" s="61">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="D34" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="G34" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="H34" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I34" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J34" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="K34" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="L34" s="59">
-        <v>3</v>
-      </c>
-      <c r="M34" s="59">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="N34" s="45">
+        <v>50</v>
+      </c>
+      <c r="N34" s="61">
         <v>100</v>
       </c>
-      <c r="O34" s="62" t="s">
+      <c r="O34" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P34" s="47">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q34" s="47">
+      <c r="P34" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q34" s="70">
         <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="R34" s="46"/>
-      <c r="S34" s="47"/>
+        <v>0.11</v>
+      </c>
+      <c r="R34" s="67"/>
+      <c r="S34" s="70"/>
     </row>
     <row r="35" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="63"/>
       <c r="B35" s="37">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="C35" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D35" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="67" t="s">
-        <v>76</v>
+      <c r="D35" s="110" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="61" t="s">
+        <v>77</v>
       </c>
       <c r="F35" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G35" s="67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H35" s="61" t="s">
         <v>152</v>
@@ -3909,17 +3956,17 @@
         <v>225</v>
       </c>
       <c r="J35" s="61" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="K35" s="68" t="s">
-        <v>196</v>
-      </c>
-      <c r="L35" s="61">
+        <v>197</v>
+      </c>
+      <c r="L35" s="111">
+        <v>2</v>
+      </c>
+      <c r="M35" s="111">
+        <f t="shared" si="0"/>
         <v>10</v>
-      </c>
-      <c r="M35" s="61">
-        <f t="shared" si="1"/>
-        <v>50</v>
       </c>
       <c r="N35" s="61">
         <v>100</v>
@@ -3937,63 +3984,63 @@
       <c r="R35" s="67"/>
       <c r="S35" s="70"/>
     </row>
-    <row r="36" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="63"/>
       <c r="B36" s="37">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D36" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="E36" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="K36" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="L36" s="61">
+        <v>17</v>
+      </c>
+      <c r="M36" s="61">
         <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="D36" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="F36" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="G36" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="H36" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I36" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J36" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="K36" s="58" t="s">
-        <v>197</v>
-      </c>
-      <c r="L36" s="59">
-        <v>2</v>
-      </c>
-      <c r="M36" s="59">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N36" s="45">
+        <v>85</v>
+      </c>
+      <c r="N36" s="61">
         <v>100</v>
       </c>
-      <c r="O36" s="62" t="s">
+      <c r="O36" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P36" s="47">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q36" s="47">
+      <c r="P36" s="70">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q36" s="70">
         <f t="shared" si="2"/>
-        <v>0.11</v>
-      </c>
-      <c r="R36" s="46"/>
-      <c r="S36" s="47"/>
-    </row>
-    <row r="37" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.06</v>
+      </c>
+      <c r="R36" s="67"/>
+      <c r="S36" s="70"/>
+    </row>
+    <row r="37" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="63"/>
       <c r="B37" s="37">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -4002,17 +4049,17 @@
       <c r="C37" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D37" s="71" t="s">
-        <v>259</v>
-      </c>
-      <c r="E37" s="67" t="s">
-        <v>78</v>
+      <c r="D37" s="110" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="61" t="s">
+        <v>79</v>
       </c>
       <c r="F37" s="61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G37" s="67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H37" s="61" t="s">
         <v>152</v>
@@ -4021,17 +4068,17 @@
         <v>225</v>
       </c>
       <c r="J37" s="61" t="s">
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="K37" s="68" t="s">
-        <v>198</v>
-      </c>
-      <c r="L37" s="61">
-        <v>17</v>
-      </c>
-      <c r="M37" s="61">
-        <f t="shared" si="1"/>
-        <v>85</v>
+        <v>199</v>
+      </c>
+      <c r="L37" s="111">
+        <v>4</v>
+      </c>
+      <c r="M37" s="111">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="N37" s="61">
         <v>100</v>
@@ -4040,541 +4087,543 @@
         <v>223</v>
       </c>
       <c r="P37" s="70">
-        <v>5.9999999999999995E-4</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q37" s="70">
         <f t="shared" si="2"/>
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="R37" s="67"/>
       <c r="S37" s="70"/>
     </row>
-    <row r="38" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" s="64" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="63"/>
       <c r="B38" s="37">
-        <f>ROW(B38) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="C38" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="D38" s="72" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="F38" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="H38" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="I38" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J38" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="K38" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="L38" s="59">
-        <v>4</v>
-      </c>
-      <c r="M38" s="59">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N38" s="45">
-        <v>100</v>
-      </c>
-      <c r="O38" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="P38" s="47">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q38" s="47">
-        <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="R38" s="46"/>
-      <c r="S38" s="47"/>
-    </row>
-    <row r="39" spans="1:19" s="64" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="I38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="J38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="K38" s="92" t="s">
+        <v>225</v>
+      </c>
+      <c r="L38" s="91">
+        <v>106</v>
+      </c>
+      <c r="M38" s="91">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="N38" s="91"/>
+      <c r="O38" s="93" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q38" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="R38" s="74"/>
+      <c r="S38" s="94"/>
+    </row>
+    <row r="39" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="63"/>
       <c r="B39" s="37">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="110" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G39" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J39" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="K39" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L39" s="111">
+        <v>1</v>
+      </c>
+      <c r="M39" s="111">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="D39" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F39" s="91" t="s">
-        <v>230</v>
-      </c>
-      <c r="G39" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="H39" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="I39" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="J39" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="K39" s="92" t="s">
-        <v>225</v>
-      </c>
-      <c r="L39" s="91">
-        <v>106</v>
-      </c>
-      <c r="M39" s="91">
-        <f t="shared" si="1"/>
-        <v>530</v>
-      </c>
-      <c r="N39" s="91"/>
-      <c r="O39" s="93" t="s">
-        <v>225</v>
-      </c>
-      <c r="P39" s="94" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q39" s="94" t="s">
-        <v>225</v>
-      </c>
-      <c r="R39" s="74"/>
-      <c r="S39" s="94"/>
-    </row>
-    <row r="40" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="N39" s="61">
+        <v>10</v>
+      </c>
+      <c r="O39" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P39" s="70">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="Q39" s="70">
+        <f t="shared" si="2"/>
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="R39" s="95"/>
+      <c r="S39" s="70"/>
+    </row>
+    <row r="40" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="63"/>
       <c r="B40" s="37">
-        <f>ROW(B40) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="C40" s="52" t="s">
-        <v>206</v>
-      </c>
-      <c r="D40" s="72" t="s">
-        <v>39</v>
-      </c>
-      <c r="E40" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" s="45" t="s">
+      <c r="C40" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="61" t="s">
         <v>230</v>
       </c>
-      <c r="G40" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="H40" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="I40" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J40" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="K40" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L40" s="59">
+      <c r="G40" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="K40" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L40" s="61">
         <v>1</v>
       </c>
-      <c r="M40" s="59">
-        <f t="shared" si="1"/>
+      <c r="M40" s="61">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N40" s="45">
-        <v>10</v>
-      </c>
-      <c r="O40" s="62" t="s">
+      <c r="N40" s="61">
+        <v>6</v>
+      </c>
+      <c r="O40" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P40" s="47">
-        <v>5.7599999999999998E-2</v>
-      </c>
-      <c r="Q40" s="47">
+      <c r="P40" s="70">
+        <v>4.1506999999999996</v>
+      </c>
+      <c r="Q40" s="70">
         <f t="shared" si="2"/>
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="R40" s="89"/>
-      <c r="S40" s="47"/>
+        <v>24.904199999999996</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="70"/>
     </row>
     <row r="41" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="63"/>
       <c r="B41" s="37">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I41" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J41" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="K41" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L41" s="111">
+        <v>8</v>
+      </c>
+      <c r="M41" s="111">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="E41" s="67" t="s">
-        <v>82</v>
-      </c>
-      <c r="F41" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="G41" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="H41" s="61" t="s">
-        <v>163</v>
-      </c>
-      <c r="I41" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="J41" s="61" t="s">
-        <v>179</v>
-      </c>
-      <c r="K41" s="68" t="s">
-        <v>225</v>
-      </c>
-      <c r="L41" s="61">
-        <v>1</v>
-      </c>
-      <c r="M41" s="61">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
       <c r="N41" s="61">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O41" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P41" s="70">
-        <v>4.1506999999999996</v>
+        <v>4.2987000000000002</v>
       </c>
       <c r="Q41" s="70">
         <f t="shared" si="2"/>
-        <v>24.904199999999996</v>
+        <v>180.5454</v>
       </c>
       <c r="R41" s="67"/>
       <c r="S41" s="70"/>
     </row>
-    <row r="42" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="63"/>
       <c r="B42" s="37">
-        <f>ROW(B42) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="72" t="s">
-        <v>41</v>
-      </c>
-      <c r="E42" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F42" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="G42" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="H42" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="I42" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J42" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="K42" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L42" s="59">
-        <v>8</v>
-      </c>
-      <c r="M42" s="59">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N42" s="45">
+      <c r="D42" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="O42" s="62" t="s">
+      <c r="E42" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="G42" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L42" s="61">
+        <v>1</v>
+      </c>
+      <c r="M42" s="61">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N42" s="61">
+        <v>6</v>
+      </c>
+      <c r="O42" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="P42" s="47">
-        <v>4.2987000000000002</v>
-      </c>
-      <c r="Q42" s="47">
+      <c r="P42" s="70">
+        <v>0.51070000000000004</v>
+      </c>
+      <c r="Q42" s="70">
         <f t="shared" si="2"/>
-        <v>180.5454</v>
-      </c>
-      <c r="R42" s="46"/>
-      <c r="S42" s="47"/>
-    </row>
-    <row r="43" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3.0642000000000005</v>
+      </c>
+      <c r="R42" s="67"/>
+      <c r="S42" s="70"/>
+    </row>
+    <row r="43" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="63"/>
       <c r="B43" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="67" t="s">
-        <v>84</v>
+      <c r="D43" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="61" t="s">
+        <v>85</v>
       </c>
       <c r="F43" s="61" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G43" s="67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H43" s="61" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I43" s="61" t="s">
         <v>225</v>
       </c>
       <c r="J43" s="61" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="K43" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L43" s="61">
+      <c r="L43" s="111">
         <v>1</v>
       </c>
-      <c r="M43" s="61">
-        <f t="shared" si="1"/>
+      <c r="M43" s="111">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N43" s="61">
         <v>6</v>
       </c>
       <c r="O43" s="69" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="P43" s="70">
-        <v>0.51070000000000004</v>
+        <v>12.6</v>
       </c>
       <c r="Q43" s="70">
         <f t="shared" si="2"/>
-        <v>3.0642000000000005</v>
-      </c>
-      <c r="R43" s="67"/>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="R43" s="95" t="s">
+        <v>269</v>
+      </c>
       <c r="S43" s="70"/>
     </row>
-    <row r="44" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="63"/>
       <c r="B44" s="37">
-        <f>ROW(B44) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="C44" s="52" t="s">
+      <c r="C44" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="G44" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="H44" s="45" t="s">
+      <c r="D44" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="G44" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="H44" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="I44" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J44" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K44" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L44" s="59">
-        <v>1</v>
-      </c>
-      <c r="M44" s="59">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N44" s="45">
-        <v>6</v>
-      </c>
-      <c r="O44" s="62" t="s">
-        <v>231</v>
-      </c>
-      <c r="P44" s="47">
-        <v>12.6</v>
-      </c>
-      <c r="Q44" s="47">
+      <c r="I44" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J44" s="61" t="s">
+        <v>233</v>
+      </c>
+      <c r="K44" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L44" s="61">
+        <v>2</v>
+      </c>
+      <c r="M44" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N44" s="61">
+        <v>11</v>
+      </c>
+      <c r="O44" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P44" s="70">
+        <v>3.8660000000000001</v>
+      </c>
+      <c r="Q44" s="70">
         <f t="shared" si="2"/>
-        <v>75.599999999999994</v>
-      </c>
-      <c r="R44" s="89" t="s">
-        <v>269</v>
-      </c>
-      <c r="S44" s="47"/>
-    </row>
-    <row r="45" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>42.526000000000003</v>
+      </c>
+      <c r="R44" s="67"/>
+      <c r="S44" s="70"/>
+    </row>
+    <row r="45" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="63"/>
       <c r="B45" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D45" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" s="67" t="s">
-        <v>86</v>
+      <c r="D45" s="110" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="61" t="s">
+        <v>87</v>
       </c>
       <c r="F45" s="61" t="s">
-        <v>240</v>
-      </c>
-      <c r="G45" s="67" t="s">
-        <v>116</v>
+        <v>241</v>
+      </c>
+      <c r="G45" s="112" t="s">
+        <v>117</v>
       </c>
       <c r="H45" s="61" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I45" s="61" t="s">
         <v>225</v>
       </c>
       <c r="J45" s="61" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="K45" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L45" s="61">
-        <v>2</v>
-      </c>
-      <c r="M45" s="61">
-        <f t="shared" si="1"/>
+      <c r="L45" s="111">
+        <v>1</v>
+      </c>
+      <c r="M45" s="111">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N45" s="61">
         <v>10</v>
       </c>
-      <c r="N45" s="61">
-        <v>11</v>
-      </c>
       <c r="O45" s="69" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="P45" s="70">
-        <v>3.8660000000000001</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="Q45" s="70">
         <f t="shared" si="2"/>
-        <v>42.526000000000003</v>
+        <v>0.63400000000000001</v>
       </c>
       <c r="R45" s="67"/>
       <c r="S45" s="70"/>
     </row>
-    <row r="46" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="63"/>
       <c r="B46" s="37">
-        <f>ROW(B46) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="72" t="s">
-        <v>45</v>
-      </c>
-      <c r="E46" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="F46" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="G46" s="98" t="s">
-        <v>117</v>
-      </c>
-      <c r="H46" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="I46" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J46" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K46" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L46" s="59">
+      <c r="D46" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="H46" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I46" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J46" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L46" s="61">
         <v>1</v>
       </c>
-      <c r="M46" s="59">
-        <f t="shared" si="1"/>
+      <c r="M46" s="61">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N46" s="45">
-        <v>10</v>
-      </c>
-      <c r="O46" s="62" t="s">
-        <v>276</v>
-      </c>
-      <c r="P46" s="47">
-        <v>6.3399999999999998E-2</v>
-      </c>
-      <c r="Q46" s="47">
+      <c r="N46" s="61">
+        <v>6</v>
+      </c>
+      <c r="O46" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P46" s="70">
+        <v>7.3</v>
+      </c>
+      <c r="Q46" s="70">
         <f t="shared" si="2"/>
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="R46" s="46"/>
-      <c r="S46" s="47"/>
+        <v>43.8</v>
+      </c>
+      <c r="R46" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="S46" s="70"/>
     </row>
     <row r="47" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="63"/>
       <c r="B47" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
       <c r="C47" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="E47" s="67" t="s">
-        <v>88</v>
+      <c r="D47" s="110" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="61" t="s">
+        <v>89</v>
       </c>
       <c r="F47" s="61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G47" s="67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H47" s="61" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I47" s="61" t="s">
         <v>225</v>
@@ -4585,300 +4634,241 @@
       <c r="K47" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L47" s="61">
-        <v>1</v>
-      </c>
-      <c r="M47" s="61">
-        <f t="shared" si="1"/>
-        <v>5</v>
+      <c r="L47" s="111">
+        <v>4</v>
+      </c>
+      <c r="M47" s="111">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="N47" s="61">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O47" s="69" t="s">
         <v>231</v>
       </c>
       <c r="P47" s="70">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q47" s="70">
         <f t="shared" si="2"/>
-        <v>43.8</v>
+        <v>88.2</v>
       </c>
       <c r="R47" s="95" t="s">
         <v>269</v>
       </c>
       <c r="S47" s="70"/>
     </row>
-    <row r="48" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" s="64" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="63"/>
       <c r="B48" s="37">
-        <f>ROW(B48) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="C48" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="F48" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="G48" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="H48" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="I48" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J48" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K48" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="L48" s="59">
-        <v>4</v>
-      </c>
-      <c r="M48" s="59">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N48" s="45">
-        <v>21</v>
-      </c>
-      <c r="O48" s="62" t="s">
-        <v>231</v>
-      </c>
-      <c r="P48" s="47">
-        <v>4.2</v>
-      </c>
-      <c r="Q48" s="47">
+      <c r="C48" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="D48" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G48" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="H48" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="I48" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J48" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="K48" s="68" t="s">
+        <v>235</v>
+      </c>
+      <c r="L48" s="61">
+        <v>1</v>
+      </c>
+      <c r="M48" s="61">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N48" s="61">
+        <v>6</v>
+      </c>
+      <c r="O48" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P48" s="70">
+        <v>0.23039999999999999</v>
+      </c>
+      <c r="Q48" s="70">
         <f t="shared" si="2"/>
-        <v>88.2</v>
-      </c>
-      <c r="R48" s="89" t="s">
-        <v>269</v>
-      </c>
-      <c r="S48" s="47"/>
+        <v>1.3824000000000001</v>
+      </c>
+      <c r="R48" s="67"/>
+      <c r="S48" s="70"/>
     </row>
     <row r="49" spans="1:19" s="64" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="63"/>
       <c r="B49" s="37">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
       <c r="C49" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="D49" s="71" t="s">
-        <v>48</v>
-      </c>
-      <c r="E49" s="67" t="s">
-        <v>90</v>
+      <c r="D49" s="110" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49" s="61" t="s">
+        <v>91</v>
       </c>
       <c r="F49" s="61" t="s">
         <v>230</v>
       </c>
       <c r="G49" s="67" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H49" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I49" s="61" t="s">
         <v>225</v>
       </c>
       <c r="J49" s="61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K49" s="68" t="s">
-        <v>235</v>
-      </c>
-      <c r="L49" s="61">
-        <v>1</v>
-      </c>
-      <c r="M49" s="61">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>237</v>
+      </c>
+      <c r="L49" s="113">
+        <v>2</v>
+      </c>
+      <c r="M49" s="113">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="N49" s="61">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O49" s="69" t="s">
         <v>223</v>
       </c>
       <c r="P49" s="70">
-        <v>0.23039999999999999</v>
+        <v>7.6899999999999996E-2</v>
       </c>
       <c r="Q49" s="70">
         <f t="shared" si="2"/>
-        <v>1.3824000000000001</v>
+        <v>1.1535</v>
       </c>
       <c r="R49" s="67"/>
       <c r="S49" s="70"/>
     </row>
-    <row r="50" spans="1:19" s="64" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="63"/>
-      <c r="B50" s="37">
-        <f>ROW(B50) - ROW($B$9)</f>
-        <v>41</v>
-      </c>
-      <c r="C50" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="D50" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E50" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="F50" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="G50" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="H50" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="I50" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J50" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="K50" s="58" t="s">
-        <v>237</v>
-      </c>
-      <c r="L50" s="75">
-        <v>2</v>
-      </c>
-      <c r="M50" s="75">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N50" s="45">
-        <v>15</v>
-      </c>
-      <c r="O50" s="62" t="s">
-        <v>223</v>
-      </c>
-      <c r="P50" s="47">
-        <v>7.6899999999999996E-2</v>
-      </c>
-      <c r="Q50" s="47">
-        <f t="shared" si="2"/>
-        <v>1.1535</v>
-      </c>
-      <c r="R50" s="46"/>
-      <c r="S50" s="47"/>
+    <row r="50" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="103" t="s">
+        <v>217</v>
+      </c>
+      <c r="O50" s="104"/>
+      <c r="P50" s="104"/>
+      <c r="Q50" s="56">
+        <f>SUM(Q10:Q49)</f>
+        <v>575.84830000000011</v>
+      </c>
+      <c r="R50" s="105"/>
+      <c r="S50" s="106"/>
     </row>
     <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="60"/>
-      <c r="M51" s="36"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
       <c r="N51" s="103" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O51" s="104"/>
       <c r="P51" s="104"/>
-      <c r="Q51" s="56">
-        <f>SUM(Q10:Q50)</f>
-        <v>580.32130000000006</v>
-      </c>
-      <c r="R51" s="105"/>
-      <c r="S51" s="106"/>
-    </row>
-    <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="103" t="s">
-        <v>218</v>
-      </c>
-      <c r="O52" s="104"/>
-      <c r="P52" s="104"/>
-      <c r="Q52" s="57">
-        <f>Q51/5</f>
-        <v>116.06426000000002</v>
-      </c>
-      <c r="R52" s="107"/>
-      <c r="S52" s="108"/>
+      <c r="Q51" s="57">
+        <f>Q50/5</f>
+        <v>115.16966000000002</v>
+      </c>
+      <c r="R51" s="107"/>
+      <c r="S51" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S51"/>
     <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S52"/>
-    <mergeCell ref="N52:P52"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O14" r:id="rId1" xr:uid="{420DCDE1-6A77-47F4-86D9-3A6544D49E88}"/>
-    <hyperlink ref="O24" r:id="rId2" xr:uid="{AEB6D0A9-124F-4BCC-BD29-0DA5FC3E1114}"/>
-    <hyperlink ref="O25" r:id="rId3" xr:uid="{75B9793B-FDE1-4887-A636-2D7648FE5B59}"/>
-    <hyperlink ref="O27" r:id="rId4" xr:uid="{8B764C3B-B8EF-4167-AB42-B04A43058B58}"/>
-    <hyperlink ref="O30" r:id="rId5" xr:uid="{337B7D6D-9EB5-4E9C-99F9-0DD2C162AB67}"/>
-    <hyperlink ref="O45" r:id="rId6" xr:uid="{D3ABA29E-C6F5-40D5-9271-A39E1BA068DB}"/>
-    <hyperlink ref="O32" r:id="rId7" xr:uid="{1CC0740B-4EB1-4CC1-85F1-43A4CEF5DC65}"/>
-    <hyperlink ref="O41" r:id="rId8" xr:uid="{CAE463F4-1476-4F54-93B4-D67CA8F283F4}"/>
-    <hyperlink ref="O36" r:id="rId9" xr:uid="{92B089EB-AA8C-4C27-8523-6B1D8A81A23B}"/>
+    <hyperlink ref="O13" r:id="rId1" xr:uid="{420DCDE1-6A77-47F4-86D9-3A6544D49E88}"/>
+    <hyperlink ref="O22" r:id="rId2" xr:uid="{AEB6D0A9-124F-4BCC-BD29-0DA5FC3E1114}"/>
+    <hyperlink ref="O23" r:id="rId3" xr:uid="{75B9793B-FDE1-4887-A636-2D7648FE5B59}"/>
+    <hyperlink ref="O26" r:id="rId4" xr:uid="{8B764C3B-B8EF-4167-AB42-B04A43058B58}"/>
+    <hyperlink ref="O29" r:id="rId5" xr:uid="{337B7D6D-9EB5-4E9C-99F9-0DD2C162AB67}"/>
+    <hyperlink ref="O44" r:id="rId6" xr:uid="{D3ABA29E-C6F5-40D5-9271-A39E1BA068DB}"/>
+    <hyperlink ref="O31" r:id="rId7" xr:uid="{1CC0740B-4EB1-4CC1-85F1-43A4CEF5DC65}"/>
+    <hyperlink ref="O40" r:id="rId8" xr:uid="{CAE463F4-1476-4F54-93B4-D67CA8F283F4}"/>
+    <hyperlink ref="O35" r:id="rId9" xr:uid="{92B089EB-AA8C-4C27-8523-6B1D8A81A23B}"/>
     <hyperlink ref="O10" r:id="rId10" xr:uid="{3F7CE80E-842A-437C-893B-FEB4182CB4E3}"/>
-    <hyperlink ref="O11" r:id="rId11" xr:uid="{9E7B7C6F-0A2E-4BCB-B35E-43B466BFDA5C}"/>
-    <hyperlink ref="O13" r:id="rId12" xr:uid="{C8CC9CA7-E92A-4BBD-A0BA-5552E9421E8B}"/>
-    <hyperlink ref="O16" r:id="rId13" xr:uid="{60ADA263-0EC7-4F8B-850D-CFEC1BEB250E}"/>
-    <hyperlink ref="O17" r:id="rId14" xr:uid="{D777C9CD-6E10-4509-97B1-7BAD3C929690}"/>
-    <hyperlink ref="O19" r:id="rId15" xr:uid="{1D337CBF-01D5-437B-B79A-CCE149CAB43B}"/>
-    <hyperlink ref="O12" r:id="rId16" xr:uid="{76A51466-FB67-4F83-972F-53D4D8CC40CB}"/>
-    <hyperlink ref="O20" r:id="rId17" xr:uid="{018B0414-39A5-4AAD-AA7D-E61B78527009}"/>
-    <hyperlink ref="O21" r:id="rId18" xr:uid="{85AD460B-7E8F-4533-84C8-49E79DFFA46F}"/>
-    <hyperlink ref="O22" r:id="rId19" xr:uid="{5936EBB3-D5EF-4BB1-8C34-4A1B869D76E0}"/>
-    <hyperlink ref="O23" r:id="rId20" xr:uid="{94935E71-5D6F-424D-AA36-F94FBA6FD350}"/>
-    <hyperlink ref="O26" r:id="rId21" xr:uid="{10D03C81-3D73-4466-AD8F-3FD074D169E1}"/>
-    <hyperlink ref="O33" r:id="rId22" xr:uid="{515FE09E-3C15-4AA6-AC28-FC6848AB4CF9}"/>
-    <hyperlink ref="O34" r:id="rId23" xr:uid="{F184C3EB-9B39-4522-A425-F5E6C8F2E2BA}"/>
-    <hyperlink ref="O35" r:id="rId24" xr:uid="{7522B420-E61D-4B13-A03E-5D2219252C19}"/>
-    <hyperlink ref="O37" r:id="rId25" xr:uid="{1FAE88F3-D29C-4196-9AA0-EC0A26F8A675}"/>
-    <hyperlink ref="O38" r:id="rId26" xr:uid="{58C63D22-D4C4-4CC6-9C17-41BAEC714A2B}"/>
-    <hyperlink ref="O42" r:id="rId27" xr:uid="{FCE98D2C-0CE3-4786-B922-305B918F7C62}"/>
-    <hyperlink ref="O43" r:id="rId28" xr:uid="{849FD330-0BAA-4388-A88F-0CB639BF150A}"/>
-    <hyperlink ref="O49" r:id="rId29" xr:uid="{2178B7AB-D5B6-4299-9DFB-A14ABFBC6872}"/>
-    <hyperlink ref="O50" r:id="rId30" xr:uid="{941D925C-D957-48A4-B614-74212814F841}"/>
-    <hyperlink ref="O15" r:id="rId31" xr:uid="{22EC1134-DF98-4938-8100-CAD056F7A6FC}"/>
-    <hyperlink ref="O18" r:id="rId32" xr:uid="{27EEC157-09A7-49ED-9980-E1E26806C989}"/>
-    <hyperlink ref="O40" r:id="rId33" xr:uid="{AE8A45B1-317C-4A4A-B10C-C532A22ED538}"/>
-    <hyperlink ref="O46" r:id="rId34" xr:uid="{DF599000-74F0-4992-8A33-6279DB7AA224}"/>
-    <hyperlink ref="O28" r:id="rId35" xr:uid="{49460E9B-A839-49B1-A25F-76DFEA3F3059}"/>
+    <hyperlink ref="O12" r:id="rId11" xr:uid="{C8CC9CA7-E92A-4BBD-A0BA-5552E9421E8B}"/>
+    <hyperlink ref="O15" r:id="rId12" xr:uid="{60ADA263-0EC7-4F8B-850D-CFEC1BEB250E}"/>
+    <hyperlink ref="O16" r:id="rId13" xr:uid="{D777C9CD-6E10-4509-97B1-7BAD3C929690}"/>
+    <hyperlink ref="O19" r:id="rId14" xr:uid="{1D337CBF-01D5-437B-B79A-CCE149CAB43B}"/>
+    <hyperlink ref="O11" r:id="rId15" xr:uid="{76A51466-FB67-4F83-972F-53D4D8CC40CB}"/>
+    <hyperlink ref="O20" r:id="rId16" xr:uid="{018B0414-39A5-4AAD-AA7D-E61B78527009}"/>
+    <hyperlink ref="O17" r:id="rId17" xr:uid="{5936EBB3-D5EF-4BB1-8C34-4A1B869D76E0}"/>
+    <hyperlink ref="O25" r:id="rId18" xr:uid="{10D03C81-3D73-4466-AD8F-3FD074D169E1}"/>
+    <hyperlink ref="O32" r:id="rId19" xr:uid="{515FE09E-3C15-4AA6-AC28-FC6848AB4CF9}"/>
+    <hyperlink ref="O33" r:id="rId20" xr:uid="{F184C3EB-9B39-4522-A425-F5E6C8F2E2BA}"/>
+    <hyperlink ref="O34" r:id="rId21" xr:uid="{7522B420-E61D-4B13-A03E-5D2219252C19}"/>
+    <hyperlink ref="O36" r:id="rId22" xr:uid="{1FAE88F3-D29C-4196-9AA0-EC0A26F8A675}"/>
+    <hyperlink ref="O37" r:id="rId23" xr:uid="{58C63D22-D4C4-4CC6-9C17-41BAEC714A2B}"/>
+    <hyperlink ref="O41" r:id="rId24" xr:uid="{FCE98D2C-0CE3-4786-B922-305B918F7C62}"/>
+    <hyperlink ref="O42" r:id="rId25" xr:uid="{849FD330-0BAA-4388-A88F-0CB639BF150A}"/>
+    <hyperlink ref="O48" r:id="rId26" xr:uid="{2178B7AB-D5B6-4299-9DFB-A14ABFBC6872}"/>
+    <hyperlink ref="O49" r:id="rId27" xr:uid="{941D925C-D957-48A4-B614-74212814F841}"/>
+    <hyperlink ref="O14" r:id="rId28" xr:uid="{22EC1134-DF98-4938-8100-CAD056F7A6FC}"/>
+    <hyperlink ref="O18" r:id="rId29" xr:uid="{27EEC157-09A7-49ED-9980-E1E26806C989}"/>
+    <hyperlink ref="O39" r:id="rId30" xr:uid="{AE8A45B1-317C-4A4A-B10C-C532A22ED538}"/>
+    <hyperlink ref="O45" r:id="rId31" xr:uid="{DF599000-74F0-4992-8A33-6279DB7AA224}"/>
+    <hyperlink ref="O27" r:id="rId32" xr:uid="{49460E9B-A839-49B1-A25F-76DFEA3F3059}"/>
+    <hyperlink ref="O21" r:id="rId33" xr:uid="{85AD460B-7E8F-4533-84C8-49E79DFFA46F}"/>
+    <hyperlink ref="O24" r:id="rId34" xr:uid="{0B162636-2BBC-4A06-BD90-D02B36D1E21F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId36"/>
+  <drawing r:id="rId35"/>
 </worksheet>
 </file>
 

--- a/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10616AFF-8CD5-4EE6-9A27-304F451BBA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03F2BF0-DA37-4BD4-BFB0-C7E91B7CC610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1716,6 +1716,21 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1746,21 +1761,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2300,15 +2300,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2358,7 +2358,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="101"/>
+      <c r="S3" s="106"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2383,7 +2383,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="102"/>
+      <c r="S4" s="107"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2408,7 +2408,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="102"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2429,7 +2429,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="102"/>
+      <c r="S6" s="107"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2450,7 +2450,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="102"/>
+      <c r="S7" s="107"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2471,7 +2471,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="102"/>
+      <c r="S8" s="107"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2651,7 +2651,7 @@
       <c r="C12" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="110" t="s">
+      <c r="D12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="61" t="s">
@@ -2675,10 +2675,10 @@
       <c r="K12" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="L12" s="111">
+      <c r="L12" s="101">
         <v>12</v>
       </c>
-      <c r="M12" s="111">
+      <c r="M12" s="101">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -2763,7 +2763,7 @@
       <c r="C14" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="110" t="s">
+      <c r="D14" s="100" t="s">
         <v>261</v>
       </c>
       <c r="E14" s="61" t="s">
@@ -2787,10 +2787,10 @@
       <c r="K14" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="L14" s="111">
+      <c r="L14" s="101">
         <v>16</v>
       </c>
-      <c r="M14" s="111">
+      <c r="M14" s="101">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
@@ -2875,7 +2875,7 @@
       <c r="C16" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="110" t="s">
+      <c r="D16" s="100" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="61" t="s">
@@ -2899,10 +2899,10 @@
       <c r="K16" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="L16" s="111">
+      <c r="L16" s="101">
         <v>6</v>
       </c>
-      <c r="M16" s="111">
+      <c r="M16" s="101">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -2987,7 +2987,7 @@
       <c r="C18" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="110" t="s">
+      <c r="D18" s="100" t="s">
         <v>277</v>
       </c>
       <c r="E18" s="67" t="s">
@@ -3043,7 +3043,7 @@
       <c r="C19" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="D19" s="100" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="61" t="s">
@@ -3067,10 +3067,10 @@
       <c r="K19" s="68" t="s">
         <v>190</v>
       </c>
-      <c r="L19" s="111">
+      <c r="L19" s="101">
         <v>4</v>
       </c>
-      <c r="M19" s="111">
+      <c r="M19" s="101">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3155,7 +3155,7 @@
       <c r="C21" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="110" t="s">
+      <c r="D21" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="61" t="s">
@@ -3179,10 +3179,10 @@
       <c r="K21" s="68" t="s">
         <v>192</v>
       </c>
-      <c r="L21" s="111">
+      <c r="L21" s="101">
         <v>8</v>
       </c>
-      <c r="M21" s="111">
+      <c r="M21" s="101">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -3211,7 +3211,7 @@
       <c r="C22" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="110" t="s">
+      <c r="D22" s="100" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="61" t="s">
@@ -3235,10 +3235,10 @@
       <c r="K22" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L22" s="111">
+      <c r="L22" s="101">
         <v>1</v>
       </c>
-      <c r="M22" s="111">
+      <c r="M22" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3322,34 +3322,34 @@
       <c r="C24" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="D24" s="109" t="s">
+      <c r="D24" s="99" t="s">
         <v>289</v>
       </c>
-      <c r="E24" s="109" t="s">
+      <c r="E24" s="99" t="s">
         <v>290</v>
       </c>
-      <c r="F24" s="109" t="s">
+      <c r="F24" s="99" t="s">
         <v>291</v>
       </c>
-      <c r="G24" s="109" t="s">
+      <c r="G24" s="99" t="s">
         <v>292</v>
       </c>
-      <c r="H24" s="109" t="s">
+      <c r="H24" s="99" t="s">
         <v>293</v>
       </c>
-      <c r="I24" s="109" t="s">
-        <v>225</v>
-      </c>
-      <c r="J24" s="109" t="s">
+      <c r="I24" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24" s="99" t="s">
         <v>294</v>
       </c>
-      <c r="K24" s="109" t="s">
-        <v>225</v>
-      </c>
-      <c r="L24" s="109">
+      <c r="K24" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="99">
         <v>2</v>
       </c>
-      <c r="M24" s="111">
+      <c r="M24" s="101">
         <f>L24*5</f>
         <v>10</v>
       </c>
@@ -3378,7 +3378,7 @@
       <c r="C25" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="110" t="s">
+      <c r="D25" s="100" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="61" t="s">
@@ -3402,10 +3402,10 @@
       <c r="K25" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L25" s="111">
+      <c r="L25" s="101">
         <v>1</v>
       </c>
-      <c r="M25" s="111">
+      <c r="M25" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3490,7 +3490,7 @@
       <c r="C27" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="110" t="s">
+      <c r="D27" s="100" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="61" t="s">
@@ -3514,10 +3514,10 @@
       <c r="K27" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L27" s="111">
+      <c r="L27" s="101">
         <v>8</v>
       </c>
-      <c r="M27" s="111">
+      <c r="M27" s="101">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -3604,7 +3604,7 @@
       <c r="C29" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="D29" s="110" t="s">
+      <c r="D29" s="100" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="61" t="s">
@@ -3628,10 +3628,10 @@
       <c r="K29" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L29" s="111">
+      <c r="L29" s="101">
         <v>1</v>
       </c>
-      <c r="M29" s="111">
+      <c r="M29" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3713,7 +3713,7 @@
       <c r="C31" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="110" t="s">
+      <c r="D31" s="100" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="61" t="s">
@@ -3737,10 +3737,10 @@
       <c r="K31" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="L31" s="111">
+      <c r="L31" s="101">
         <v>3</v>
       </c>
-      <c r="M31" s="111">
+      <c r="M31" s="101">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3825,7 +3825,7 @@
       <c r="C33" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D33" s="110" t="s">
+      <c r="D33" s="100" t="s">
         <v>34</v>
       </c>
       <c r="E33" s="61" t="s">
@@ -3849,10 +3849,10 @@
       <c r="K33" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="L33" s="111">
+      <c r="L33" s="101">
         <v>3</v>
       </c>
-      <c r="M33" s="111">
+      <c r="M33" s="101">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3937,7 +3937,7 @@
       <c r="C35" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D35" s="110" t="s">
+      <c r="D35" s="100" t="s">
         <v>36</v>
       </c>
       <c r="E35" s="61" t="s">
@@ -3961,10 +3961,10 @@
       <c r="K35" s="68" t="s">
         <v>197</v>
       </c>
-      <c r="L35" s="111">
+      <c r="L35" s="101">
         <v>2</v>
       </c>
-      <c r="M35" s="111">
+      <c r="M35" s="101">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -4049,7 +4049,7 @@
       <c r="C37" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D37" s="110" t="s">
+      <c r="D37" s="100" t="s">
         <v>37</v>
       </c>
       <c r="E37" s="61" t="s">
@@ -4073,10 +4073,10 @@
       <c r="K37" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="L37" s="111">
+      <c r="L37" s="101">
         <v>4</v>
       </c>
-      <c r="M37" s="111">
+      <c r="M37" s="101">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -4158,7 +4158,7 @@
       <c r="C39" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="D39" s="110" t="s">
+      <c r="D39" s="100" t="s">
         <v>39</v>
       </c>
       <c r="E39" s="61" t="s">
@@ -4182,10 +4182,10 @@
       <c r="K39" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L39" s="111">
+      <c r="L39" s="101">
         <v>1</v>
       </c>
-      <c r="M39" s="111">
+      <c r="M39" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4270,7 +4270,7 @@
       <c r="C41" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="110" t="s">
+      <c r="D41" s="100" t="s">
         <v>41</v>
       </c>
       <c r="E41" s="61" t="s">
@@ -4294,10 +4294,10 @@
       <c r="K41" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L41" s="111">
+      <c r="L41" s="101">
         <v>8</v>
       </c>
-      <c r="M41" s="111">
+      <c r="M41" s="101">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="C43" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="110" t="s">
+      <c r="D43" s="100" t="s">
         <v>43</v>
       </c>
       <c r="E43" s="61" t="s">
@@ -4406,10 +4406,10 @@
       <c r="K43" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L43" s="111">
+      <c r="L43" s="101">
         <v>1</v>
       </c>
-      <c r="M43" s="111">
+      <c r="M43" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="C45" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D45" s="110" t="s">
+      <c r="D45" s="100" t="s">
         <v>45</v>
       </c>
       <c r="E45" s="61" t="s">
@@ -4505,7 +4505,7 @@
       <c r="F45" s="61" t="s">
         <v>241</v>
       </c>
-      <c r="G45" s="112" t="s">
+      <c r="G45" s="102" t="s">
         <v>117</v>
       </c>
       <c r="H45" s="61" t="s">
@@ -4520,10 +4520,10 @@
       <c r="K45" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L45" s="111">
+      <c r="L45" s="101">
         <v>1</v>
       </c>
-      <c r="M45" s="111">
+      <c r="M45" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4610,7 +4610,7 @@
       <c r="C47" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="110" t="s">
+      <c r="D47" s="100" t="s">
         <v>47</v>
       </c>
       <c r="E47" s="61" t="s">
@@ -4634,10 +4634,10 @@
       <c r="K47" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="L47" s="111">
+      <c r="L47" s="101">
         <v>4</v>
       </c>
-      <c r="M47" s="111">
+      <c r="M47" s="101">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -4724,7 +4724,7 @@
       <c r="C49" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="D49" s="110" t="s">
+      <c r="D49" s="100" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="61" t="s">
@@ -4748,10 +4748,10 @@
       <c r="K49" s="68" t="s">
         <v>237</v>
       </c>
-      <c r="L49" s="113">
+      <c r="L49" s="103">
         <v>2</v>
       </c>
-      <c r="M49" s="113">
+      <c r="M49" s="103">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -4785,17 +4785,17 @@
       <c r="K50" s="36"/>
       <c r="L50" s="60"/>
       <c r="M50" s="36"/>
-      <c r="N50" s="103" t="s">
+      <c r="N50" s="108" t="s">
         <v>217</v>
       </c>
-      <c r="O50" s="104"/>
-      <c r="P50" s="104"/>
+      <c r="O50" s="109"/>
+      <c r="P50" s="109"/>
       <c r="Q50" s="56">
         <f>SUM(Q10:Q49)</f>
         <v>575.84830000000011</v>
       </c>
-      <c r="R50" s="105"/>
-      <c r="S50" s="106"/>
+      <c r="R50" s="110"/>
+      <c r="S50" s="111"/>
     </row>
     <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -4811,17 +4811,17 @@
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
       <c r="M51" s="10"/>
-      <c r="N51" s="103" t="s">
+      <c r="N51" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="O51" s="104"/>
-      <c r="P51" s="104"/>
+      <c r="O51" s="109"/>
+      <c r="P51" s="109"/>
       <c r="Q51" s="57">
         <f>Q50/5</f>
         <v>115.16966000000002</v>
       </c>
-      <c r="R51" s="107"/>
-      <c r="S51" s="108"/>
+      <c r="R51" s="112"/>
+      <c r="S51" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4908,15 +4908,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4966,7 +4966,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="101"/>
+      <c r="S3" s="106"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4991,7 +4991,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="102"/>
+      <c r="S4" s="107"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5016,7 +5016,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="102"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5037,7 +5037,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="102"/>
+      <c r="S6" s="107"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5058,7 +5058,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="102"/>
+      <c r="S7" s="107"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5079,7 +5079,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="102"/>
+      <c r="S8" s="107"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -7452,17 +7452,17 @@
       <c r="K51" s="36"/>
       <c r="L51" s="60"/>
       <c r="M51" s="36"/>
-      <c r="N51" s="103" t="s">
+      <c r="N51" s="108" t="s">
         <v>217</v>
       </c>
-      <c r="O51" s="104"/>
-      <c r="P51" s="104"/>
+      <c r="O51" s="109"/>
+      <c r="P51" s="109"/>
       <c r="Q51" s="56">
         <f>SUM(Q10:Q50)</f>
         <v>2278.0145999999995</v>
       </c>
-      <c r="R51" s="105"/>
-      <c r="S51" s="106"/>
+      <c r="R51" s="110"/>
+      <c r="S51" s="111"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -7478,17 +7478,17 @@
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
-      <c r="N52" s="103" t="s">
+      <c r="N52" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="O52" s="104"/>
-      <c r="P52" s="104"/>
+      <c r="O52" s="109"/>
+      <c r="P52" s="109"/>
       <c r="Q52" s="57">
         <f>Q51/20</f>
         <v>113.90072999999998</v>
       </c>
-      <c r="R52" s="107"/>
-      <c r="S52" s="108"/>
+      <c r="R52" s="112"/>
+      <c r="S52" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7576,15 +7576,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -7634,7 +7634,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="101"/>
+      <c r="S3" s="106"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -7659,7 +7659,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="102"/>
+      <c r="S4" s="107"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -7684,7 +7684,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="102"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -7705,7 +7705,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="102"/>
+      <c r="S6" s="107"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -7726,7 +7726,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="102"/>
+      <c r="S7" s="107"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -7747,7 +7747,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="102"/>
+      <c r="S8" s="107"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -10132,17 +10132,17 @@
       <c r="K51" s="36"/>
       <c r="L51" s="60"/>
       <c r="M51" s="36"/>
-      <c r="N51" s="103" t="s">
+      <c r="N51" s="108" t="s">
         <v>217</v>
       </c>
-      <c r="O51" s="104"/>
-      <c r="P51" s="104"/>
+      <c r="O51" s="109"/>
+      <c r="P51" s="109"/>
       <c r="Q51" s="56">
         <f>SUM(Q10:Q50)</f>
         <v>70390.64899999999</v>
       </c>
-      <c r="R51" s="105"/>
-      <c r="S51" s="106"/>
+      <c r="R51" s="110"/>
+      <c r="S51" s="111"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -10158,17 +10158,17 @@
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
-      <c r="N52" s="103" t="s">
+      <c r="N52" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="O52" s="104"/>
-      <c r="P52" s="104"/>
+      <c r="O52" s="109"/>
+      <c r="P52" s="109"/>
       <c r="Q52" s="57">
         <f>Q51/1000</f>
         <v>70.390648999999996</v>
       </c>
-      <c r="R52" s="107"/>
-      <c r="S52" s="108"/>
+      <c r="R52" s="112"/>
+      <c r="S52" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10418,15 +10418,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -10476,7 +10476,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="101"/>
+      <c r="S3" s="106"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -10501,7 +10501,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="102"/>
+      <c r="S4" s="107"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -10526,7 +10526,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="102"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -10547,7 +10547,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="102"/>
+      <c r="S6" s="107"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -10568,7 +10568,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="102"/>
+      <c r="S7" s="107"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -10589,7 +10589,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="102"/>
+      <c r="S8" s="107"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -12960,17 +12960,17 @@
       <c r="K51" s="36"/>
       <c r="L51" s="60"/>
       <c r="M51" s="36"/>
-      <c r="N51" s="103" t="s">
+      <c r="N51" s="108" t="s">
         <v>217</v>
       </c>
-      <c r="O51" s="104"/>
-      <c r="P51" s="104"/>
+      <c r="O51" s="109"/>
+      <c r="P51" s="109"/>
       <c r="Q51" s="56">
         <f>SUM(Q10:Q50)</f>
         <v>305315.783</v>
       </c>
-      <c r="R51" s="105"/>
-      <c r="S51" s="106"/>
+      <c r="R51" s="110"/>
+      <c r="S51" s="111"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -12986,17 +12986,17 @@
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
-      <c r="N52" s="103" t="s">
+      <c r="N52" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="O52" s="104"/>
-      <c r="P52" s="104"/>
+      <c r="O52" s="109"/>
+      <c r="P52" s="109"/>
       <c r="Q52" s="57">
         <f>Q51/5000</f>
         <v>61.063156599999999</v>
       </c>
-      <c r="R52" s="107"/>
-      <c r="S52" s="108"/>
+      <c r="R52" s="112"/>
+      <c r="S52" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03F2BF0-DA37-4BD4-BFB0-C7E91B7CC610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="4" r:id="rId1"/>
-    <sheet name="20 Boards " sheetId="1" r:id="rId2"/>
-    <sheet name="1K Boards" sheetId="2" r:id="rId3"/>
-    <sheet name="5K Boards" sheetId="3" r:id="rId4"/>
+    <sheet name="10 Boards" sheetId="5" r:id="rId2"/>
+    <sheet name="20 Boards " sheetId="1" r:id="rId3"/>
+    <sheet name="1K Boards" sheetId="2" r:id="rId4"/>
+    <sheet name="5K Boards" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="300">
   <si>
     <t>Component list</t>
   </si>
@@ -900,9 +900,6 @@
     <t>C45, C46, C47, C48, C49, C50, C51, C52, C97, C100, C101, C102, C103, C104, C105, C106, C107, C119, C122, C123, C126, C130, C133, C134, C141, C142, C143, C144, C145, C146, C147, C148, C149, C150, C151, C152, C153, C154, C155, C156, C157, C158, C159, C160, C161, C162, C163, C164</t>
   </si>
   <si>
-    <t>C2168289</t>
-  </si>
-  <si>
     <t>Ferrite Bead</t>
   </si>
   <si>
@@ -925,12 +922,27 @@
   </si>
   <si>
     <t>C1,C2, C23, C26, C28, C137, C138, C139, C140</t>
+  </si>
+  <si>
+    <t>Quantity (10 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (10 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (10 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (10 Boards)</t>
+  </si>
+  <si>
+    <t>C62892</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1848,6 +1860,60 @@
       <xdr:col>18</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
+      <xdr:rowOff>10416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1743075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB3A8A17-4845-4B09-9856-ACE6C9FE1054}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18307050" y="620016"/>
+          <a:ext cx="1733550" cy="1084959"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -1895,7 +1961,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1949,7 +2015,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2265,7 +2331,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C605574B-18B4-4F8A-BF86-58CC88FF11BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2540,7 +2606,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E10" s="67" t="s">
         <v>51</v>
@@ -3006,7 +3072,7 @@
         <v>225</v>
       </c>
       <c r="J18" s="61" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="K18" s="68" t="s">
         <v>189</v>
@@ -3320,28 +3386,28 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" s="99" t="s">
         <v>288</v>
       </c>
-      <c r="D24" s="99" t="s">
+      <c r="E24" s="99" t="s">
         <v>289</v>
       </c>
-      <c r="E24" s="99" t="s">
+      <c r="F24" s="99" t="s">
         <v>290</v>
       </c>
-      <c r="F24" s="99" t="s">
+      <c r="G24" s="99" t="s">
         <v>291</v>
       </c>
-      <c r="G24" s="99" t="s">
+      <c r="H24" s="99" t="s">
         <v>292</v>
       </c>
-      <c r="H24" s="99" t="s">
+      <c r="I24" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24" s="99" t="s">
         <v>293</v>
-      </c>
-      <c r="I24" s="99" t="s">
-        <v>225</v>
-      </c>
-      <c r="J24" s="99" t="s">
-        <v>294</v>
       </c>
       <c r="K24" s="99" t="s">
         <v>225</v>
@@ -4515,7 +4581,7 @@
         <v>225</v>
       </c>
       <c r="J45" s="61" t="s">
-        <v>225</v>
+        <v>299</v>
       </c>
       <c r="K45" s="68" t="s">
         <v>225</v>
@@ -4531,14 +4597,14 @@
         <v>10</v>
       </c>
       <c r="O45" s="69" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="P45" s="70">
-        <v>6.3399999999999998E-2</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="Q45" s="70">
         <f t="shared" si="2"/>
-        <v>0.63400000000000001</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="R45" s="67"/>
       <c r="S45" s="70"/>
@@ -4792,7 +4858,7 @@
       <c r="P50" s="109"/>
       <c r="Q50" s="56">
         <f>SUM(Q10:Q49)</f>
-        <v>575.84830000000011</v>
+        <v>575.70330000000001</v>
       </c>
       <c r="R50" s="110"/>
       <c r="S50" s="111"/>
@@ -4818,7 +4884,7 @@
       <c r="P51" s="109"/>
       <c r="Q51" s="57">
         <f>Q50/5</f>
-        <v>115.16966000000002</v>
+        <v>115.14066</v>
       </c>
       <c r="R51" s="112"/>
       <c r="S51" s="113"/>
@@ -4832,40 +4898,40 @@
     <mergeCell ref="N51:P51"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O13" r:id="rId1" xr:uid="{420DCDE1-6A77-47F4-86D9-3A6544D49E88}"/>
-    <hyperlink ref="O22" r:id="rId2" xr:uid="{AEB6D0A9-124F-4BCC-BD29-0DA5FC3E1114}"/>
-    <hyperlink ref="O23" r:id="rId3" xr:uid="{75B9793B-FDE1-4887-A636-2D7648FE5B59}"/>
-    <hyperlink ref="O26" r:id="rId4" xr:uid="{8B764C3B-B8EF-4167-AB42-B04A43058B58}"/>
-    <hyperlink ref="O29" r:id="rId5" xr:uid="{337B7D6D-9EB5-4E9C-99F9-0DD2C162AB67}"/>
-    <hyperlink ref="O44" r:id="rId6" xr:uid="{D3ABA29E-C6F5-40D5-9271-A39E1BA068DB}"/>
-    <hyperlink ref="O31" r:id="rId7" xr:uid="{1CC0740B-4EB1-4CC1-85F1-43A4CEF5DC65}"/>
-    <hyperlink ref="O40" r:id="rId8" xr:uid="{CAE463F4-1476-4F54-93B4-D67CA8F283F4}"/>
-    <hyperlink ref="O35" r:id="rId9" xr:uid="{92B089EB-AA8C-4C27-8523-6B1D8A81A23B}"/>
-    <hyperlink ref="O10" r:id="rId10" xr:uid="{3F7CE80E-842A-437C-893B-FEB4182CB4E3}"/>
-    <hyperlink ref="O12" r:id="rId11" xr:uid="{C8CC9CA7-E92A-4BBD-A0BA-5552E9421E8B}"/>
-    <hyperlink ref="O15" r:id="rId12" xr:uid="{60ADA263-0EC7-4F8B-850D-CFEC1BEB250E}"/>
-    <hyperlink ref="O16" r:id="rId13" xr:uid="{D777C9CD-6E10-4509-97B1-7BAD3C929690}"/>
-    <hyperlink ref="O19" r:id="rId14" xr:uid="{1D337CBF-01D5-437B-B79A-CCE149CAB43B}"/>
-    <hyperlink ref="O11" r:id="rId15" xr:uid="{76A51466-FB67-4F83-972F-53D4D8CC40CB}"/>
-    <hyperlink ref="O20" r:id="rId16" xr:uid="{018B0414-39A5-4AAD-AA7D-E61B78527009}"/>
-    <hyperlink ref="O17" r:id="rId17" xr:uid="{5936EBB3-D5EF-4BB1-8C34-4A1B869D76E0}"/>
-    <hyperlink ref="O25" r:id="rId18" xr:uid="{10D03C81-3D73-4466-AD8F-3FD074D169E1}"/>
-    <hyperlink ref="O32" r:id="rId19" xr:uid="{515FE09E-3C15-4AA6-AC28-FC6848AB4CF9}"/>
-    <hyperlink ref="O33" r:id="rId20" xr:uid="{F184C3EB-9B39-4522-A425-F5E6C8F2E2BA}"/>
-    <hyperlink ref="O34" r:id="rId21" xr:uid="{7522B420-E61D-4B13-A03E-5D2219252C19}"/>
-    <hyperlink ref="O36" r:id="rId22" xr:uid="{1FAE88F3-D29C-4196-9AA0-EC0A26F8A675}"/>
-    <hyperlink ref="O37" r:id="rId23" xr:uid="{58C63D22-D4C4-4CC6-9C17-41BAEC714A2B}"/>
-    <hyperlink ref="O41" r:id="rId24" xr:uid="{FCE98D2C-0CE3-4786-B922-305B918F7C62}"/>
-    <hyperlink ref="O42" r:id="rId25" xr:uid="{849FD330-0BAA-4388-A88F-0CB639BF150A}"/>
-    <hyperlink ref="O48" r:id="rId26" xr:uid="{2178B7AB-D5B6-4299-9DFB-A14ABFBC6872}"/>
-    <hyperlink ref="O49" r:id="rId27" xr:uid="{941D925C-D957-48A4-B614-74212814F841}"/>
-    <hyperlink ref="O14" r:id="rId28" xr:uid="{22EC1134-DF98-4938-8100-CAD056F7A6FC}"/>
-    <hyperlink ref="O18" r:id="rId29" xr:uid="{27EEC157-09A7-49ED-9980-E1E26806C989}"/>
-    <hyperlink ref="O39" r:id="rId30" xr:uid="{AE8A45B1-317C-4A4A-B10C-C532A22ED538}"/>
-    <hyperlink ref="O45" r:id="rId31" xr:uid="{DF599000-74F0-4992-8A33-6279DB7AA224}"/>
-    <hyperlink ref="O27" r:id="rId32" xr:uid="{49460E9B-A839-49B1-A25F-76DFEA3F3059}"/>
-    <hyperlink ref="O21" r:id="rId33" xr:uid="{85AD460B-7E8F-4533-84C8-49E79DFFA46F}"/>
-    <hyperlink ref="O24" r:id="rId34" xr:uid="{0B162636-2BBC-4A06-BD90-D02B36D1E21F}"/>
+    <hyperlink ref="O13" r:id="rId1"/>
+    <hyperlink ref="O22" r:id="rId2"/>
+    <hyperlink ref="O23" r:id="rId3"/>
+    <hyperlink ref="O26" r:id="rId4"/>
+    <hyperlink ref="O29" r:id="rId5"/>
+    <hyperlink ref="O44" r:id="rId6"/>
+    <hyperlink ref="O31" r:id="rId7"/>
+    <hyperlink ref="O40" r:id="rId8"/>
+    <hyperlink ref="O35" r:id="rId9"/>
+    <hyperlink ref="O10" r:id="rId10"/>
+    <hyperlink ref="O12" r:id="rId11"/>
+    <hyperlink ref="O15" r:id="rId12"/>
+    <hyperlink ref="O16" r:id="rId13"/>
+    <hyperlink ref="O19" r:id="rId14"/>
+    <hyperlink ref="O11" r:id="rId15"/>
+    <hyperlink ref="O20" r:id="rId16"/>
+    <hyperlink ref="O17" r:id="rId17"/>
+    <hyperlink ref="O25" r:id="rId18"/>
+    <hyperlink ref="O32" r:id="rId19"/>
+    <hyperlink ref="O33" r:id="rId20"/>
+    <hyperlink ref="O34" r:id="rId21"/>
+    <hyperlink ref="O36" r:id="rId22"/>
+    <hyperlink ref="O37" r:id="rId23"/>
+    <hyperlink ref="O41" r:id="rId24"/>
+    <hyperlink ref="O42" r:id="rId25"/>
+    <hyperlink ref="O48" r:id="rId26"/>
+    <hyperlink ref="O49" r:id="rId27"/>
+    <hyperlink ref="O14" r:id="rId28"/>
+    <hyperlink ref="O18" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O27" r:id="rId31"/>
+    <hyperlink ref="O21" r:id="rId32"/>
+    <hyperlink ref="O24" r:id="rId33"/>
+    <hyperlink ref="O45" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId35"/>
@@ -4873,7 +4939,2619 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="106"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="107"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="107"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="107"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="107"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="107"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="R9" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="63"/>
+      <c r="B10" s="37">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>294</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="K10" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="L10" s="61">
+        <v>9</v>
+      </c>
+      <c r="M10" s="61">
+        <f>L10*10</f>
+        <v>90</v>
+      </c>
+      <c r="N10" s="61">
+        <v>100</v>
+      </c>
+      <c r="O10" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" s="70">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="Q10" s="70">
+        <f>P10*N10</f>
+        <v>2.36</v>
+      </c>
+      <c r="R10" s="67"/>
+      <c r="S10" s="70"/>
+    </row>
+    <row r="11" spans="1:19" s="64" customFormat="1" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="63"/>
+      <c r="B11" s="37">
+        <f>ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="K11" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="L11" s="61">
+        <v>51</v>
+      </c>
+      <c r="M11" s="61">
+        <f t="shared" ref="M11:M49" si="0">L11*10</f>
+        <v>510</v>
+      </c>
+      <c r="N11" s="61">
+        <v>550</v>
+      </c>
+      <c r="O11" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P11" s="70">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="Q11" s="70">
+        <f>P11*N11</f>
+        <v>4.2350000000000003</v>
+      </c>
+      <c r="R11" s="67"/>
+      <c r="S11" s="70"/>
+    </row>
+    <row r="12" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="63"/>
+      <c r="B12" s="37">
+        <f t="shared" ref="B12:B48" si="1">ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="100" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="K12" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="L12" s="101">
+        <v>12</v>
+      </c>
+      <c r="M12" s="61">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="N12" s="61">
+        <v>200</v>
+      </c>
+      <c r="O12" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P12" s="70">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q12" s="70">
+        <f t="shared" ref="Q12:Q49" si="2">P12*N12</f>
+        <v>0.5</v>
+      </c>
+      <c r="R12" s="67"/>
+      <c r="S12" s="70"/>
+    </row>
+    <row r="13" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="63"/>
+      <c r="B13" s="37">
+        <f>ROW(B13) - ROW($B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="K13" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="L13" s="61">
+        <v>2</v>
+      </c>
+      <c r="M13" s="61">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N13" s="61">
+        <v>21</v>
+      </c>
+      <c r="O13" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P13" s="70">
+        <v>1.2005999999999999</v>
+      </c>
+      <c r="Q13" s="70">
+        <f t="shared" si="2"/>
+        <v>25.212599999999998</v>
+      </c>
+      <c r="R13" s="67"/>
+      <c r="S13" s="70"/>
+    </row>
+    <row r="14" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="63"/>
+      <c r="B14" s="37">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="100" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>262</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>263</v>
+      </c>
+      <c r="K14" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="L14" s="101">
+        <v>16</v>
+      </c>
+      <c r="M14" s="61">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="N14" s="61">
+        <v>200</v>
+      </c>
+      <c r="O14" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P14" s="70">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q14" s="70">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="R14" s="67"/>
+      <c r="S14" s="70"/>
+    </row>
+    <row r="15" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="63"/>
+      <c r="B15" s="37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>246</v>
+      </c>
+      <c r="K15" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="L15" s="61">
+        <v>1</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N15" s="61">
+        <v>20</v>
+      </c>
+      <c r="O15" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P15" s="70">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="Q15" s="70">
+        <f t="shared" si="2"/>
+        <v>0.754</v>
+      </c>
+      <c r="R15" s="67"/>
+      <c r="S15" s="70"/>
+    </row>
+    <row r="16" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="63"/>
+      <c r="B16" s="37">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="100" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>247</v>
+      </c>
+      <c r="K16" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="L16" s="101">
+        <v>6</v>
+      </c>
+      <c r="M16" s="61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="N16" s="61">
+        <v>100</v>
+      </c>
+      <c r="O16" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P16" s="70">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q16" s="70">
+        <f t="shared" si="2"/>
+        <v>0.27</v>
+      </c>
+      <c r="R16" s="67"/>
+      <c r="S16" s="70"/>
+    </row>
+    <row r="17" spans="1:19" s="64" customFormat="1" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="63"/>
+      <c r="B17" s="37">
+        <f>ROW(B17) - ROW($B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J17" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="L17" s="61">
+        <v>48</v>
+      </c>
+      <c r="M17" s="61">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="N17" s="61">
+        <v>500</v>
+      </c>
+      <c r="O17" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P17" s="70">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q17" s="70">
+        <f>P17*N17</f>
+        <v>0.6</v>
+      </c>
+      <c r="R17" s="67"/>
+      <c r="S17" s="70"/>
+    </row>
+    <row r="18" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="63"/>
+      <c r="B18" s="37">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="100" t="s">
+        <v>277</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>265</v>
+      </c>
+      <c r="K18" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="L18" s="61">
+        <v>11</v>
+      </c>
+      <c r="M18" s="61">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="N18" s="61">
+        <v>120</v>
+      </c>
+      <c r="O18" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P18" s="70">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="Q18" s="70">
+        <f>P18*N18</f>
+        <v>4.3559999999999999</v>
+      </c>
+      <c r="R18" s="67"/>
+      <c r="S18" s="70"/>
+    </row>
+    <row r="19" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="63"/>
+      <c r="B19" s="37">
+        <f>ROW(B19) - ROW($B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="100" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="K19" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="L19" s="101">
+        <v>4</v>
+      </c>
+      <c r="M19" s="61">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N19" s="61">
+        <v>100</v>
+      </c>
+      <c r="O19" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P19" s="70">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q19" s="70">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="R19" s="67"/>
+      <c r="S19" s="70"/>
+    </row>
+    <row r="20" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="63"/>
+      <c r="B20" s="37">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J20" s="61" t="s">
+        <v>248</v>
+      </c>
+      <c r="K20" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="L20" s="61">
+        <v>1</v>
+      </c>
+      <c r="M20" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N20" s="61">
+        <v>100</v>
+      </c>
+      <c r="O20" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P20" s="70">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q20" s="70">
+        <f t="shared" si="2"/>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="R20" s="67"/>
+      <c r="S20" s="70"/>
+    </row>
+    <row r="21" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="63"/>
+      <c r="B21" s="37">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="100" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J21" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="K21" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="L21" s="101">
+        <v>8</v>
+      </c>
+      <c r="M21" s="61">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="N21" s="61">
+        <v>100</v>
+      </c>
+      <c r="O21" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P21" s="70">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q21" s="70">
+        <f t="shared" si="2"/>
+        <v>0.27</v>
+      </c>
+      <c r="R21" s="67"/>
+      <c r="S21" s="70"/>
+    </row>
+    <row r="22" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="63"/>
+      <c r="B22" s="37">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="K22" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L22" s="101">
+        <v>1</v>
+      </c>
+      <c r="M22" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N22" s="61">
+        <v>20</v>
+      </c>
+      <c r="O22" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P22" s="70">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="Q22" s="70">
+        <f t="shared" si="2"/>
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="R22" s="67"/>
+      <c r="S22" s="70"/>
+    </row>
+    <row r="23" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="63"/>
+      <c r="B23" s="37">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="K23" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L23" s="61">
+        <v>1</v>
+      </c>
+      <c r="M23" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N23" s="61">
+        <v>20</v>
+      </c>
+      <c r="O23" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P23" s="70">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="Q23" s="70">
+        <f t="shared" si="2"/>
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="R23" s="67"/>
+      <c r="S23" s="70"/>
+    </row>
+    <row r="24" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="63"/>
+      <c r="B24" s="37">
+        <v>15</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" s="99" t="s">
+        <v>288</v>
+      </c>
+      <c r="E24" s="99" t="s">
+        <v>289</v>
+      </c>
+      <c r="F24" s="99" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" s="99" t="s">
+        <v>291</v>
+      </c>
+      <c r="H24" s="99" t="s">
+        <v>292</v>
+      </c>
+      <c r="I24" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24" s="99" t="s">
+        <v>293</v>
+      </c>
+      <c r="K24" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="99">
+        <v>2</v>
+      </c>
+      <c r="M24" s="61">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N24" s="61">
+        <v>40</v>
+      </c>
+      <c r="O24" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P24" s="70">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q24" s="70">
+        <f>P24*N24</f>
+        <v>1.288</v>
+      </c>
+      <c r="R24" s="67"/>
+      <c r="S24" s="70"/>
+    </row>
+    <row r="25" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="63"/>
+      <c r="B25" s="37">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="74" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="J25" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="K25" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L25" s="101">
+        <v>1</v>
+      </c>
+      <c r="M25" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="61">
+        <v>20</v>
+      </c>
+      <c r="O25" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P25" s="70">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q25" s="70">
+        <f t="shared" si="2"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R25" s="67"/>
+      <c r="S25" s="70"/>
+    </row>
+    <row r="26" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="63"/>
+      <c r="B26" s="37">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L26" s="61">
+        <v>1</v>
+      </c>
+      <c r="M26" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N26" s="61">
+        <v>20</v>
+      </c>
+      <c r="O26" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P26" s="70">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="Q26" s="70">
+        <f t="shared" si="2"/>
+        <v>1.1119999999999999</v>
+      </c>
+      <c r="R26" s="67"/>
+      <c r="S26" s="70"/>
+    </row>
+    <row r="27" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="63"/>
+      <c r="B27" s="37">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K27" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L27" s="101">
+        <v>8</v>
+      </c>
+      <c r="M27" s="61">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="N27" s="61">
+        <v>85</v>
+      </c>
+      <c r="O27" s="69" t="s">
+        <v>276</v>
+      </c>
+      <c r="P27" s="70">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="Q27" s="70">
+        <f t="shared" si="2"/>
+        <v>71.995000000000005</v>
+      </c>
+      <c r="R27" s="95"/>
+      <c r="S27" s="70"/>
+    </row>
+    <row r="28" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="63"/>
+      <c r="B28" s="37">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K28" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L28" s="61">
+        <v>4</v>
+      </c>
+      <c r="M28" s="61">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N28" s="61">
+        <v>45</v>
+      </c>
+      <c r="O28" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P28" s="70">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="70">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="R28" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="S28" s="70"/>
+    </row>
+    <row r="29" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="63"/>
+      <c r="B29" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="100" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="74">
+        <v>61300611121</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="J29" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="K29" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L29" s="101">
+        <v>1</v>
+      </c>
+      <c r="M29" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="61">
+        <v>20</v>
+      </c>
+      <c r="O29" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P29" s="70">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="Q29" s="70">
+        <f t="shared" si="2"/>
+        <v>0.66</v>
+      </c>
+      <c r="R29" s="67"/>
+      <c r="S29" s="70"/>
+    </row>
+    <row r="30" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="63"/>
+      <c r="B30" s="37">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="I30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="J30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="K30" s="92" t="s">
+        <v>225</v>
+      </c>
+      <c r="L30" s="91">
+        <v>5</v>
+      </c>
+      <c r="M30" s="61">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="N30" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="O30" s="93" t="s">
+        <v>225</v>
+      </c>
+      <c r="P30" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q30" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="R30" s="74"/>
+      <c r="S30" s="94"/>
+    </row>
+    <row r="31" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="63"/>
+      <c r="B31" s="37">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="74" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="J31" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="K31" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="L31" s="101">
+        <v>3</v>
+      </c>
+      <c r="M31" s="61">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="N31" s="61">
+        <v>100</v>
+      </c>
+      <c r="O31" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P31" s="70">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q31" s="70">
+        <f t="shared" si="2"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R31" s="67"/>
+      <c r="S31" s="70"/>
+    </row>
+    <row r="32" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="63"/>
+      <c r="B32" s="37">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>250</v>
+      </c>
+      <c r="K32" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="L32" s="61">
+        <v>8</v>
+      </c>
+      <c r="M32" s="61">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="N32" s="61">
+        <v>100</v>
+      </c>
+      <c r="O32" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P32" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q32" s="70">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="R32" s="67"/>
+      <c r="S32" s="70"/>
+    </row>
+    <row r="33" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="63"/>
+      <c r="B33" s="37">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" s="100" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="G33" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="H33" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I33" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J33" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="K33" s="68" t="s">
+        <v>195</v>
+      </c>
+      <c r="L33" s="101">
+        <v>3</v>
+      </c>
+      <c r="M33" s="61">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="N33" s="61">
+        <v>100</v>
+      </c>
+      <c r="O33" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P33" s="70">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q33" s="70">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="R33" s="67"/>
+      <c r="S33" s="70"/>
+    </row>
+    <row r="34" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="63"/>
+      <c r="B34" s="37">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="L34" s="61">
+        <v>10</v>
+      </c>
+      <c r="M34" s="61">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="N34" s="61">
+        <v>200</v>
+      </c>
+      <c r="O34" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P34" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q34" s="70">
+        <f t="shared" si="2"/>
+        <v>0.22</v>
+      </c>
+      <c r="R34" s="67"/>
+      <c r="S34" s="70"/>
+    </row>
+    <row r="35" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="63"/>
+      <c r="B35" s="37">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" s="100" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="H35" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I35" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J35" s="61" t="s">
+        <v>243</v>
+      </c>
+      <c r="K35" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="L35" s="101">
+        <v>2</v>
+      </c>
+      <c r="M35" s="61">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N35" s="61">
+        <v>100</v>
+      </c>
+      <c r="O35" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P35" s="70">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q35" s="70">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="R35" s="67"/>
+      <c r="S35" s="70"/>
+    </row>
+    <row r="36" spans="1:19" s="64" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="63"/>
+      <c r="B36" s="37">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D36" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="E36" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="K36" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="L36" s="61">
+        <v>17</v>
+      </c>
+      <c r="M36" s="61">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="N36" s="61">
+        <v>200</v>
+      </c>
+      <c r="O36" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P36" s="70">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q36" s="70">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="R36" s="67"/>
+      <c r="S36" s="70"/>
+    </row>
+    <row r="37" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="63"/>
+      <c r="B37" s="37">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D37" s="100" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G37" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="H37" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J37" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="K37" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="L37" s="101">
+        <v>4</v>
+      </c>
+      <c r="M37" s="61">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N37" s="61">
+        <v>100</v>
+      </c>
+      <c r="O37" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P37" s="70">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q37" s="70">
+        <f t="shared" si="2"/>
+        <v>0.13</v>
+      </c>
+      <c r="R37" s="67"/>
+      <c r="S37" s="70"/>
+    </row>
+    <row r="38" spans="1:19" s="64" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="63"/>
+      <c r="B38" s="37">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="I38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="J38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="K38" s="92" t="s">
+        <v>225</v>
+      </c>
+      <c r="L38" s="91">
+        <v>106</v>
+      </c>
+      <c r="M38" s="91">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="N38" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="O38" s="93" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q38" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="R38" s="74"/>
+      <c r="S38" s="94"/>
+    </row>
+    <row r="39" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="63"/>
+      <c r="B39" s="37">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G39" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J39" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="K39" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L39" s="101">
+        <v>1</v>
+      </c>
+      <c r="M39" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N39" s="61">
+        <v>20</v>
+      </c>
+      <c r="O39" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P39" s="70">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="Q39" s="70">
+        <f t="shared" si="2"/>
+        <v>1.1260000000000001</v>
+      </c>
+      <c r="R39" s="95"/>
+      <c r="S39" s="70"/>
+    </row>
+    <row r="40" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="63"/>
+      <c r="B40" s="37">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="K40" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L40" s="61">
+        <v>1</v>
+      </c>
+      <c r="M40" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N40" s="61">
+        <v>11</v>
+      </c>
+      <c r="O40" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P40" s="70">
+        <v>4.1506999999999996</v>
+      </c>
+      <c r="Q40" s="70">
+        <f t="shared" si="2"/>
+        <v>45.657699999999998</v>
+      </c>
+      <c r="R40" s="67"/>
+      <c r="S40" s="70"/>
+    </row>
+    <row r="41" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="63"/>
+      <c r="B41" s="37">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I41" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J41" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="K41" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L41" s="101">
+        <v>8</v>
+      </c>
+      <c r="M41" s="61">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="N41" s="61">
+        <v>81</v>
+      </c>
+      <c r="O41" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P41" s="70">
+        <v>4.2987000000000002</v>
+      </c>
+      <c r="Q41" s="70">
+        <f t="shared" si="2"/>
+        <v>348.19470000000001</v>
+      </c>
+      <c r="R41" s="67"/>
+      <c r="S41" s="70"/>
+    </row>
+    <row r="42" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="63"/>
+      <c r="B42" s="37">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="G42" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L42" s="61">
+        <v>1</v>
+      </c>
+      <c r="M42" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N42" s="61">
+        <v>11</v>
+      </c>
+      <c r="O42" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P42" s="70">
+        <v>0.35959999999999998</v>
+      </c>
+      <c r="Q42" s="70">
+        <f t="shared" si="2"/>
+        <v>3.9555999999999996</v>
+      </c>
+      <c r="R42" s="67"/>
+      <c r="S42" s="70"/>
+    </row>
+    <row r="43" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="63"/>
+      <c r="B43" s="37">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I43" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J43" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K43" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L43" s="101">
+        <v>1</v>
+      </c>
+      <c r="M43" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N43" s="61">
+        <v>11</v>
+      </c>
+      <c r="O43" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P43" s="70">
+        <v>12.6</v>
+      </c>
+      <c r="Q43" s="70">
+        <f t="shared" si="2"/>
+        <v>138.6</v>
+      </c>
+      <c r="R43" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="S43" s="70"/>
+    </row>
+    <row r="44" spans="1:19" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="63"/>
+      <c r="B44" s="37">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="G44" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="H44" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I44" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J44" s="61" t="s">
+        <v>233</v>
+      </c>
+      <c r="K44" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L44" s="61">
+        <v>2</v>
+      </c>
+      <c r="M44" s="61">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N44" s="61">
+        <v>21</v>
+      </c>
+      <c r="O44" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P44" s="70">
+        <v>3.9996</v>
+      </c>
+      <c r="Q44" s="70">
+        <f t="shared" si="2"/>
+        <v>83.991600000000005</v>
+      </c>
+      <c r="R44" s="67"/>
+      <c r="S44" s="70"/>
+    </row>
+    <row r="45" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="63"/>
+      <c r="B45" s="37">
+        <f>ROW(B45) - ROW($B$9)</f>
+        <v>36</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="G45" s="102" t="s">
+        <v>117</v>
+      </c>
+      <c r="H45" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="I45" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J45" s="61" t="s">
+        <v>299</v>
+      </c>
+      <c r="K45" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L45" s="101">
+        <v>1</v>
+      </c>
+      <c r="M45" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N45" s="61">
+        <v>20</v>
+      </c>
+      <c r="O45" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P45" s="70">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="Q45" s="70">
+        <f t="shared" si="2"/>
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="R45" s="67"/>
+      <c r="S45" s="70"/>
+    </row>
+    <row r="46" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="63"/>
+      <c r="B46" s="37">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="H46" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="I46" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J46" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L46" s="61">
+        <v>1</v>
+      </c>
+      <c r="M46" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N46" s="61">
+        <v>11</v>
+      </c>
+      <c r="O46" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P46" s="70">
+        <v>7.3</v>
+      </c>
+      <c r="Q46" s="70">
+        <f t="shared" si="2"/>
+        <v>80.3</v>
+      </c>
+      <c r="R46" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="S46" s="70"/>
+    </row>
+    <row r="47" spans="1:19" s="64" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="63"/>
+      <c r="B47" s="37">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="100" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="H47" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="I47" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J47" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="K47" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L47" s="101">
+        <v>4</v>
+      </c>
+      <c r="M47" s="61">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="N47" s="61">
+        <v>41</v>
+      </c>
+      <c r="O47" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P47" s="70">
+        <v>4.2</v>
+      </c>
+      <c r="Q47" s="70">
+        <f t="shared" si="2"/>
+        <v>172.20000000000002</v>
+      </c>
+      <c r="R47" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="S47" s="70"/>
+    </row>
+    <row r="48" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="63"/>
+      <c r="B48" s="37">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="D48" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G48" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="H48" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="I48" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J48" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="K48" s="68" t="s">
+        <v>235</v>
+      </c>
+      <c r="L48" s="61">
+        <v>1</v>
+      </c>
+      <c r="M48" s="61">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N48" s="61">
+        <v>15</v>
+      </c>
+      <c r="O48" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P48" s="70">
+        <v>0.2301</v>
+      </c>
+      <c r="Q48" s="70">
+        <f t="shared" si="2"/>
+        <v>3.4514999999999998</v>
+      </c>
+      <c r="R48" s="67"/>
+      <c r="S48" s="70"/>
+    </row>
+    <row r="49" spans="1:19" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="63"/>
+      <c r="B49" s="37">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="D49" s="100" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G49" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="H49" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="I49" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J49" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="K49" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="L49" s="103">
+        <v>2</v>
+      </c>
+      <c r="M49" s="61">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N49" s="61">
+        <v>25</v>
+      </c>
+      <c r="O49" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="P49" s="70">
+        <v>7.5300000000000006E-2</v>
+      </c>
+      <c r="Q49" s="70">
+        <f t="shared" si="2"/>
+        <v>1.8825000000000001</v>
+      </c>
+      <c r="R49" s="67"/>
+      <c r="S49" s="70"/>
+    </row>
+    <row r="50" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="108" t="s">
+        <v>217</v>
+      </c>
+      <c r="O50" s="109"/>
+      <c r="P50" s="109"/>
+      <c r="Q50" s="56">
+        <f>SUM(Q10:Q49)</f>
+        <v>1087.9541999999997</v>
+      </c>
+      <c r="R50" s="110"/>
+      <c r="S50" s="111"/>
+    </row>
+    <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="108" t="s">
+        <v>218</v>
+      </c>
+      <c r="O51" s="109"/>
+      <c r="P51" s="109"/>
+      <c r="Q51" s="57">
+        <f>Q50/10</f>
+        <v>108.79541999999996</v>
+      </c>
+      <c r="R51" s="112"/>
+      <c r="S51" s="113"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S51"/>
+    <mergeCell ref="N51:P51"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O13" r:id="rId1"/>
+    <hyperlink ref="O22" r:id="rId2"/>
+    <hyperlink ref="O23" r:id="rId3"/>
+    <hyperlink ref="O26" r:id="rId4"/>
+    <hyperlink ref="O29" r:id="rId5"/>
+    <hyperlink ref="O44" r:id="rId6"/>
+    <hyperlink ref="O31" r:id="rId7"/>
+    <hyperlink ref="O40" r:id="rId8"/>
+    <hyperlink ref="O35" r:id="rId9"/>
+    <hyperlink ref="O10" r:id="rId10"/>
+    <hyperlink ref="O12" r:id="rId11"/>
+    <hyperlink ref="O15" r:id="rId12"/>
+    <hyperlink ref="O16" r:id="rId13"/>
+    <hyperlink ref="O19" r:id="rId14"/>
+    <hyperlink ref="O11" r:id="rId15"/>
+    <hyperlink ref="O20" r:id="rId16"/>
+    <hyperlink ref="O17" r:id="rId17"/>
+    <hyperlink ref="O25" r:id="rId18"/>
+    <hyperlink ref="O32" r:id="rId19"/>
+    <hyperlink ref="O33" r:id="rId20"/>
+    <hyperlink ref="O34" r:id="rId21"/>
+    <hyperlink ref="O36" r:id="rId22"/>
+    <hyperlink ref="O37" r:id="rId23"/>
+    <hyperlink ref="O41" r:id="rId24"/>
+    <hyperlink ref="O42" r:id="rId25"/>
+    <hyperlink ref="O48" r:id="rId26"/>
+    <hyperlink ref="O49" r:id="rId27"/>
+    <hyperlink ref="O14" r:id="rId28"/>
+    <hyperlink ref="O18" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O27" r:id="rId31"/>
+    <hyperlink ref="O21" r:id="rId32"/>
+    <hyperlink ref="O24" r:id="rId33"/>
+    <hyperlink ref="O45" r:id="rId34"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId35"/>
+  <drawing r:id="rId36"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7499,40 +10177,40 @@
     <mergeCell ref="N52:P52"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O14" r:id="rId1" xr:uid="{736BD189-760A-4B09-A3F6-F664DCC7E819}"/>
-    <hyperlink ref="O24" r:id="rId2" xr:uid="{1F81CF20-471E-4E25-91A1-ACADE372D7F1}"/>
-    <hyperlink ref="O25" r:id="rId3" xr:uid="{1FFF2F14-D016-403D-B7DE-3461C5CEE3CC}"/>
-    <hyperlink ref="O27" r:id="rId4" xr:uid="{A67D8B75-ADCA-454A-90A2-7B3827ED99FF}"/>
-    <hyperlink ref="O30" r:id="rId5" xr:uid="{2156ACCA-5D51-4A13-B679-1A5F84AF210C}"/>
-    <hyperlink ref="O45" r:id="rId6" xr:uid="{E3681D50-BCF6-45BF-92E2-FA79AE9F7F63}"/>
-    <hyperlink ref="O32" r:id="rId7" xr:uid="{708B72BB-8155-435C-A98A-443BAD0793CE}"/>
-    <hyperlink ref="O41" r:id="rId8" xr:uid="{5A47B33C-2078-42A0-97CB-FDA2AEFAD03A}"/>
-    <hyperlink ref="O36" r:id="rId9" xr:uid="{69A12946-F47E-4DFE-985E-8D4693A7CC10}"/>
-    <hyperlink ref="O10" r:id="rId10" xr:uid="{8FDB36E3-3359-4086-A00B-9B44E30AE660}"/>
-    <hyperlink ref="O11" r:id="rId11" xr:uid="{3348A2EA-3BD0-47EE-8D96-64F7519EA682}"/>
-    <hyperlink ref="O13" r:id="rId12" xr:uid="{F6C212B2-15D4-464A-A620-9DC42777AB26}"/>
-    <hyperlink ref="O16" r:id="rId13" xr:uid="{6C5E3693-5C77-457F-8D07-198366E2398D}"/>
-    <hyperlink ref="O17" r:id="rId14" xr:uid="{53C23FF1-FE99-4B67-B6FF-04B3CB1B9110}"/>
-    <hyperlink ref="O19" r:id="rId15" xr:uid="{7B46B2C0-14AE-4B4E-805C-D393B1A50D70}"/>
-    <hyperlink ref="O12" r:id="rId16" xr:uid="{382FF0FA-7010-4BD6-B83E-B24898DEAFC2}"/>
-    <hyperlink ref="O20" r:id="rId17" xr:uid="{AE531983-D06C-4C60-B45D-E4544B04C394}"/>
-    <hyperlink ref="O21" r:id="rId18" xr:uid="{45297EE2-EE7D-4B4F-A3C8-9A5E031EF4B4}"/>
-    <hyperlink ref="O22" r:id="rId19" xr:uid="{0DAF9DCD-55F7-4DC6-A56C-F28831022179}"/>
-    <hyperlink ref="O23" r:id="rId20" xr:uid="{175B306F-E9B1-4F1E-AD1F-3E90011CB1AA}"/>
-    <hyperlink ref="O26" r:id="rId21" xr:uid="{B770F765-5335-487F-9967-272DD1C9A2E1}"/>
-    <hyperlink ref="O33" r:id="rId22" xr:uid="{0D74FD7F-A6AB-421A-8F10-7C11981AF05F}"/>
-    <hyperlink ref="O34" r:id="rId23" xr:uid="{57959F40-302E-4C7E-BCCB-DC9E117DC9C9}"/>
-    <hyperlink ref="O35" r:id="rId24" xr:uid="{6D489768-7C07-4E89-B8C4-B27785A5ACC4}"/>
-    <hyperlink ref="O37" r:id="rId25" xr:uid="{421CEA32-ED48-4D99-ADE3-24AC8291EFF0}"/>
-    <hyperlink ref="O38" r:id="rId26" xr:uid="{8AD47C0D-DD20-446B-99FD-D1C94B901710}"/>
-    <hyperlink ref="O42" r:id="rId27" xr:uid="{39F5D6FC-B79E-4A23-A4F5-F94AE19CCF54}"/>
-    <hyperlink ref="O43" r:id="rId28" xr:uid="{26F56D36-5160-4F93-B0FE-BA5D7F279576}"/>
-    <hyperlink ref="O49" r:id="rId29" xr:uid="{0141DE74-1F28-4DA9-B73A-7BD298437E30}"/>
-    <hyperlink ref="O50" r:id="rId30" xr:uid="{71472283-ADCE-419D-B345-3F78D4C9B4A1}"/>
-    <hyperlink ref="O15" r:id="rId31" xr:uid="{386A98B2-E463-46C3-98CA-031EE3ACAF7E}"/>
-    <hyperlink ref="O18" r:id="rId32" xr:uid="{3F640406-EF82-415C-B941-ACDE17CD6FD1}"/>
-    <hyperlink ref="O40" r:id="rId33" xr:uid="{43DD3F14-DD7D-4C17-951A-197F63191CA8}"/>
-    <hyperlink ref="O46" r:id="rId34" xr:uid="{948A3EC2-41ED-496E-AA82-E4BD496EE4E9}"/>
+    <hyperlink ref="O14" r:id="rId1"/>
+    <hyperlink ref="O24" r:id="rId2"/>
+    <hyperlink ref="O25" r:id="rId3"/>
+    <hyperlink ref="O27" r:id="rId4"/>
+    <hyperlink ref="O30" r:id="rId5"/>
+    <hyperlink ref="O45" r:id="rId6"/>
+    <hyperlink ref="O32" r:id="rId7"/>
+    <hyperlink ref="O41" r:id="rId8"/>
+    <hyperlink ref="O36" r:id="rId9"/>
+    <hyperlink ref="O10" r:id="rId10"/>
+    <hyperlink ref="O11" r:id="rId11"/>
+    <hyperlink ref="O13" r:id="rId12"/>
+    <hyperlink ref="O16" r:id="rId13"/>
+    <hyperlink ref="O17" r:id="rId14"/>
+    <hyperlink ref="O19" r:id="rId15"/>
+    <hyperlink ref="O12" r:id="rId16"/>
+    <hyperlink ref="O20" r:id="rId17"/>
+    <hyperlink ref="O21" r:id="rId18"/>
+    <hyperlink ref="O22" r:id="rId19"/>
+    <hyperlink ref="O23" r:id="rId20"/>
+    <hyperlink ref="O26" r:id="rId21"/>
+    <hyperlink ref="O33" r:id="rId22"/>
+    <hyperlink ref="O34" r:id="rId23"/>
+    <hyperlink ref="O35" r:id="rId24"/>
+    <hyperlink ref="O37" r:id="rId25"/>
+    <hyperlink ref="O38" r:id="rId26"/>
+    <hyperlink ref="O42" r:id="rId27"/>
+    <hyperlink ref="O43" r:id="rId28"/>
+    <hyperlink ref="O49" r:id="rId29"/>
+    <hyperlink ref="O50" r:id="rId30"/>
+    <hyperlink ref="O15" r:id="rId31"/>
+    <hyperlink ref="O18" r:id="rId32"/>
+    <hyperlink ref="O40" r:id="rId33"/>
+    <hyperlink ref="O46" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
@@ -7540,8 +10218,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0680A4D2-3D39-4CFF-92FF-477EAC1CAE20}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10263,36 +12941,36 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="O14" r:id="rId1" xr:uid="{3F666622-19CD-49D8-836D-A715AF8C7BCB}"/>
-    <hyperlink ref="O24" r:id="rId2" xr:uid="{70905355-4C57-456D-9862-DFE0DD3DB964}"/>
-    <hyperlink ref="O25" r:id="rId3" xr:uid="{86986251-3D2A-4A7C-A416-3D1199C223D0}"/>
-    <hyperlink ref="O27" r:id="rId4" xr:uid="{375CEA92-3EB9-4829-BD66-68D717A59027}"/>
-    <hyperlink ref="O30" r:id="rId5" xr:uid="{F6949712-ED65-4C77-96E9-47E5044BB43D}"/>
-    <hyperlink ref="O45" r:id="rId6" xr:uid="{730F629A-9B2F-4B72-926C-B3532D45F489}"/>
-    <hyperlink ref="O32" r:id="rId7" xr:uid="{D108523B-8283-4FDF-9170-5BCD9B14CB7B}"/>
-    <hyperlink ref="O36" r:id="rId8" xr:uid="{DA6F1F5A-17F0-4592-9BBF-67B5057A6A77}"/>
-    <hyperlink ref="O10" r:id="rId9" xr:uid="{4D1847F1-01A3-44D8-A3EE-C7D9202B4A5A}"/>
-    <hyperlink ref="O11" r:id="rId10" xr:uid="{2A13FAAE-C51F-4AE7-915C-559FF7F93908}"/>
-    <hyperlink ref="O13" r:id="rId11" xr:uid="{2BE82DA5-AC48-4568-BB81-F34A8E1B1D52}"/>
-    <hyperlink ref="O16" r:id="rId12" xr:uid="{B305E14A-3565-4C71-9EE7-98BA68FFD6C9}"/>
-    <hyperlink ref="O17" r:id="rId13" xr:uid="{0C952D0E-7AB2-4D03-8DC7-8D34D7AB5CFE}"/>
-    <hyperlink ref="O19" r:id="rId14" xr:uid="{565A9792-A268-4B63-9EF1-6DFC64627684}"/>
-    <hyperlink ref="O12" r:id="rId15" xr:uid="{11F996D3-01E5-4AF3-9786-E6E069221F62}"/>
-    <hyperlink ref="O20" r:id="rId16" xr:uid="{7EA3CEF5-E0E6-497A-9663-E94D6D4E58EA}"/>
-    <hyperlink ref="O21" r:id="rId17" xr:uid="{22EEA227-D865-482D-A540-A9B3310DF171}"/>
-    <hyperlink ref="O22" r:id="rId18" xr:uid="{B3BC910E-3C07-4957-BCD7-862D3FE44DCC}"/>
-    <hyperlink ref="O23" r:id="rId19" xr:uid="{17A9BDF4-CAAF-49F1-8D54-44697239E78B}"/>
-    <hyperlink ref="O26" r:id="rId20" xr:uid="{8BA4993F-EF8D-4853-9AAF-4D944F6F9318}"/>
-    <hyperlink ref="O33" r:id="rId21" xr:uid="{76F393FA-22D5-4682-BBA7-E03DE74678BE}"/>
-    <hyperlink ref="O34" r:id="rId22" xr:uid="{C3D3E8F5-250D-420F-A560-8FFEE7977CE4}"/>
-    <hyperlink ref="O35" r:id="rId23" xr:uid="{BE7D3710-9F89-4332-A6A2-6ECB3E8D552C}"/>
-    <hyperlink ref="O37" r:id="rId24" xr:uid="{D44A97AB-9CCA-4520-94CC-47254B3DBCF7}"/>
-    <hyperlink ref="O38" r:id="rId25" xr:uid="{5BF77E5E-22E7-47C4-A6AA-CE2094986432}"/>
-    <hyperlink ref="O43" r:id="rId26" xr:uid="{766B6931-E141-41BD-90BC-14A8A9662E42}"/>
-    <hyperlink ref="O49" r:id="rId27" xr:uid="{A08941E2-E59B-4E31-9A9E-7D3C3FA152D0}"/>
-    <hyperlink ref="O50" r:id="rId28" xr:uid="{3384746F-1328-4509-B5D1-3A3DA916D396}"/>
-    <hyperlink ref="O15" r:id="rId29" xr:uid="{4032D33F-E07C-4164-91A3-C25F8D36C2F6}"/>
-    <hyperlink ref="O18" r:id="rId30" xr:uid="{BC60AEA0-E2CE-478D-8549-567D3F944642}"/>
+    <hyperlink ref="O14" r:id="rId1"/>
+    <hyperlink ref="O24" r:id="rId2"/>
+    <hyperlink ref="O25" r:id="rId3"/>
+    <hyperlink ref="O27" r:id="rId4"/>
+    <hyperlink ref="O30" r:id="rId5"/>
+    <hyperlink ref="O45" r:id="rId6"/>
+    <hyperlink ref="O32" r:id="rId7"/>
+    <hyperlink ref="O36" r:id="rId8"/>
+    <hyperlink ref="O10" r:id="rId9"/>
+    <hyperlink ref="O11" r:id="rId10"/>
+    <hyperlink ref="O13" r:id="rId11"/>
+    <hyperlink ref="O16" r:id="rId12"/>
+    <hyperlink ref="O17" r:id="rId13"/>
+    <hyperlink ref="O19" r:id="rId14"/>
+    <hyperlink ref="O12" r:id="rId15"/>
+    <hyperlink ref="O20" r:id="rId16"/>
+    <hyperlink ref="O21" r:id="rId17"/>
+    <hyperlink ref="O22" r:id="rId18"/>
+    <hyperlink ref="O23" r:id="rId19"/>
+    <hyperlink ref="O26" r:id="rId20"/>
+    <hyperlink ref="O33" r:id="rId21"/>
+    <hyperlink ref="O34" r:id="rId22"/>
+    <hyperlink ref="O35" r:id="rId23"/>
+    <hyperlink ref="O37" r:id="rId24"/>
+    <hyperlink ref="O38" r:id="rId25"/>
+    <hyperlink ref="O43" r:id="rId26"/>
+    <hyperlink ref="O49" r:id="rId27"/>
+    <hyperlink ref="O50" r:id="rId28"/>
+    <hyperlink ref="O15" r:id="rId29"/>
+    <hyperlink ref="O18" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId31"/>
@@ -10384,8 +13062,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169C7114-0090-4126-B55D-94BB641514CB}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13091,36 +15769,36 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="O24" r:id="rId1" xr:uid="{A27C862F-18F0-414E-AA8D-2898A66A92FE}"/>
-    <hyperlink ref="O25" r:id="rId2" xr:uid="{6FBFD1C4-482C-455A-AFDA-16DD91F590C0}"/>
-    <hyperlink ref="O27" r:id="rId3" xr:uid="{CF64CBB6-FC18-4CB1-87A0-4111CB47E3E1}"/>
-    <hyperlink ref="O30" r:id="rId4" xr:uid="{158427D7-D8CA-43FE-AFFB-EF9BA9336FF0}"/>
-    <hyperlink ref="O45" r:id="rId5" xr:uid="{56CEDD64-C5D3-4056-9F8A-E6CF4236300C}"/>
-    <hyperlink ref="O32" r:id="rId6" xr:uid="{3EC30965-8FF2-4122-92ED-196F57D35EA1}"/>
-    <hyperlink ref="O36" r:id="rId7" xr:uid="{E09E614F-0B24-4621-95CC-32DE85E40D90}"/>
-    <hyperlink ref="O26" r:id="rId8" xr:uid="{ACB6F6A4-0C21-4DBD-9962-B15DF1B7367E}"/>
-    <hyperlink ref="O33" r:id="rId9" xr:uid="{FB317990-9A6D-468C-9FD1-D6CF2B2835D8}"/>
-    <hyperlink ref="O34" r:id="rId10" xr:uid="{7FDD2B95-AAE1-4720-A377-0691A800B3EB}"/>
-    <hyperlink ref="O35" r:id="rId11" xr:uid="{80B13D6B-62B5-4925-BF28-902E9C5DBB14}"/>
-    <hyperlink ref="O37" r:id="rId12" xr:uid="{5DC89305-5A5D-4C98-8CDC-999B45CE207A}"/>
-    <hyperlink ref="O38" r:id="rId13" xr:uid="{F0954EE6-EB24-40B5-951D-CDF505B8A795}"/>
-    <hyperlink ref="O43" r:id="rId14" xr:uid="{49544DB8-79A0-4AD4-B110-6458441F3A9F}"/>
-    <hyperlink ref="O49" r:id="rId15" xr:uid="{D770D024-E5D2-4683-97A4-B80BAC74C6DF}"/>
-    <hyperlink ref="O50" r:id="rId16" xr:uid="{74D85B11-B2EF-42DB-A13B-8E5F2C7D65C5}"/>
-    <hyperlink ref="O14" r:id="rId17" xr:uid="{1CB83DFC-54F3-4028-8E1E-09418CA64831}"/>
-    <hyperlink ref="O10" r:id="rId18" xr:uid="{11C0AA53-3CC1-4CA8-BC8E-EA79C5F6C391}"/>
-    <hyperlink ref="O11" r:id="rId19" xr:uid="{6A106D2F-3961-4EDE-8F12-FA92C3426ECE}"/>
-    <hyperlink ref="O13" r:id="rId20" xr:uid="{B9EF9F33-7141-4884-A0CF-836FC7A92669}"/>
-    <hyperlink ref="O16" r:id="rId21" xr:uid="{5755DACF-36D9-40E4-B729-6401E1EFD638}"/>
-    <hyperlink ref="O17" r:id="rId22" xr:uid="{FA68E91E-7971-4D93-8266-262F4B8C76B1}"/>
-    <hyperlink ref="O19" r:id="rId23" xr:uid="{AB54CD27-A0ED-430E-931E-2E3BB2779236}"/>
-    <hyperlink ref="O12" r:id="rId24" xr:uid="{E0442F91-7A7C-45AC-95E5-79180D190660}"/>
-    <hyperlink ref="O20" r:id="rId25" xr:uid="{AEC25953-76C7-4CFC-AD0E-399D1C1BECD1}"/>
-    <hyperlink ref="O21" r:id="rId26" xr:uid="{3B547896-B09A-4F1E-B377-CAE4E72962A5}"/>
-    <hyperlink ref="O22" r:id="rId27" xr:uid="{35646BB1-5AA8-4C6F-B76E-EC8444B771AF}"/>
-    <hyperlink ref="O23" r:id="rId28" xr:uid="{A4139BCF-83A8-42C9-8FEE-2A5B55572CD0}"/>
-    <hyperlink ref="O15" r:id="rId29" xr:uid="{6C4052E8-5365-49C8-94FF-FDF3A71A90A6}"/>
-    <hyperlink ref="O18" r:id="rId30" xr:uid="{F3175E97-F14C-4B7F-A205-C10794218E90}"/>
+    <hyperlink ref="O24" r:id="rId1"/>
+    <hyperlink ref="O25" r:id="rId2"/>
+    <hyperlink ref="O27" r:id="rId3"/>
+    <hyperlink ref="O30" r:id="rId4"/>
+    <hyperlink ref="O45" r:id="rId5"/>
+    <hyperlink ref="O32" r:id="rId6"/>
+    <hyperlink ref="O36" r:id="rId7"/>
+    <hyperlink ref="O26" r:id="rId8"/>
+    <hyperlink ref="O33" r:id="rId9"/>
+    <hyperlink ref="O34" r:id="rId10"/>
+    <hyperlink ref="O35" r:id="rId11"/>
+    <hyperlink ref="O37" r:id="rId12"/>
+    <hyperlink ref="O38" r:id="rId13"/>
+    <hyperlink ref="O43" r:id="rId14"/>
+    <hyperlink ref="O49" r:id="rId15"/>
+    <hyperlink ref="O50" r:id="rId16"/>
+    <hyperlink ref="O14" r:id="rId17"/>
+    <hyperlink ref="O10" r:id="rId18"/>
+    <hyperlink ref="O11" r:id="rId19"/>
+    <hyperlink ref="O13" r:id="rId20"/>
+    <hyperlink ref="O16" r:id="rId21"/>
+    <hyperlink ref="O17" r:id="rId22"/>
+    <hyperlink ref="O19" r:id="rId23"/>
+    <hyperlink ref="O12" r:id="rId24"/>
+    <hyperlink ref="O20" r:id="rId25"/>
+    <hyperlink ref="O21" r:id="rId26"/>
+    <hyperlink ref="O22" r:id="rId27"/>
+    <hyperlink ref="O23" r:id="rId28"/>
+    <hyperlink ref="O15" r:id="rId29"/>
+    <hyperlink ref="O18" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId31"/>
